--- a/W3_LSPC_Watershed/inputs/Project_Control_Mattole.xlsx
+++ b/W3_LSPC_Watershed/inputs/Project_Control_Mattole.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88EB0120-FFFA-4358-B3FF-0113FB351A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33CF025-8814-4D88-95DD-118C6F334615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="83">
   <si>
     <t>cimis_id</t>
   </si>
@@ -281,6 +281,12 @@
     <t>staged/gage</t>
   </si>
   <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>raw/gage/other</t>
+  </si>
+  <si>
     <t>../data/shared</t>
   </si>
   <si>
@@ -320,9 +326,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -698,12 +705,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7E96793-80A0-4E7D-B9B3-D183DF1A597C}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.44140625" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="59.88671875" customWidth="1"/>
+    <col min="4" max="4" width="98" customWidth="1"/>
     <col min="5" max="5" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -735,7 +742,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -803,7 +810,7 @@
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -882,13 +889,13 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -902,10 +909,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -919,10 +926,10 @@
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -933,13 +940,13 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -953,10 +960,10 @@
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -967,13 +974,13 @@
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
         <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -984,13 +991,13 @@
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -1004,12 +1011,29 @@
         <v>35</v>
       </c>
       <c r="C18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
         <v>45</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D19" t="s">
         <v>46</v>
       </c>
-      <c r="E18" t="b">
+      <c r="E19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1021,8 +1045,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807B5B57-87AE-4381-98BD-5313FE53BAA3}">
-  <dimension ref="A1:C138"/>
+  <dimension ref="A1:N138"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="12" max="12" width="9.109375" style="2"/>
+    <col min="13" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1037,35 +1065,35 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>58531</v>
+        <v>58532</v>
       </c>
       <c r="B2">
-        <v>39.923743405510798</v>
+        <v>39.924490133429103</v>
       </c>
       <c r="C2">
-        <v>-123.94529507586</v>
+        <v>-123.921907643062</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>58532</v>
+        <v>58531</v>
       </c>
       <c r="B3">
-        <v>39.924490133429103</v>
+        <v>39.923743405510798</v>
       </c>
       <c r="C3">
-        <v>-123.921907643062</v>
+        <v>-123.94529507586</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>57531</v>
+        <v>57534</v>
       </c>
       <c r="B4">
-        <v>39.9597185725206</v>
+        <v>39.961946598247202</v>
       </c>
       <c r="C4">
-        <v>-123.947243597701</v>
+        <v>-123.87704529454599</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1081,101 +1109,101 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>57029</v>
+        <v>57531</v>
       </c>
       <c r="B6">
-        <v>39.976198533925903</v>
+        <v>39.9597185725206</v>
       </c>
       <c r="C6">
-        <v>-123.995026579648</v>
+        <v>-123.947243597701</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>57534</v>
+        <v>57029</v>
       </c>
       <c r="B7">
-        <v>39.961946598247202</v>
+        <v>39.976198533925903</v>
       </c>
       <c r="C7">
-        <v>-123.87704529454599</v>
+        <v>-123.995026579648</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>56532</v>
+        <v>56534</v>
       </c>
       <c r="B8">
-        <v>39.996442081465801</v>
+        <v>39.997923760351497</v>
       </c>
       <c r="C8">
-        <v>-123.92578355145599</v>
+        <v>-123.878961132055</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>56531</v>
+        <v>56532</v>
       </c>
       <c r="B9">
-        <v>39.9956945798018</v>
+        <v>39.996442081465801</v>
       </c>
       <c r="C9">
-        <v>-123.94919404407</v>
+        <v>-123.92578355145599</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>56534</v>
+        <v>56531</v>
       </c>
       <c r="B10">
-        <v>39.997923760351497</v>
+        <v>39.9956945798018</v>
       </c>
       <c r="C10">
-        <v>-123.878961132055</v>
+        <v>-123.94919404407</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>56028</v>
+        <v>56529</v>
       </c>
       <c r="B11">
-        <v>40.011413162802903</v>
+        <v>39.994186252748399</v>
       </c>
       <c r="C11">
-        <v>-124.02041587925299</v>
+        <v>-123.99601358092301</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>56529</v>
+        <v>56028</v>
       </c>
       <c r="B12">
-        <v>39.994186252748399</v>
+        <v>40.011413162802903</v>
       </c>
       <c r="C12">
-        <v>-123.99601358092301</v>
+        <v>-124.02041587925299</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>55532</v>
+        <v>55534</v>
       </c>
       <c r="B13">
-        <v>40.032419332703199</v>
+        <v>40.033901780593901</v>
       </c>
       <c r="C13">
-        <v>-123.927724378265</v>
+        <v>-123.88087886286</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>55027</v>
+        <v>55532</v>
       </c>
       <c r="B14">
-        <v>40.046623419514702</v>
+        <v>40.032419332703199</v>
       </c>
       <c r="C14">
-        <v>-124.045829739881</v>
+        <v>-123.927724378265</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -1191,24 +1219,24 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>55534</v>
+        <v>55029</v>
       </c>
       <c r="B16">
-        <v>40.033901780593901</v>
+        <v>40.0481506989724</v>
       </c>
       <c r="C16">
-        <v>-123.88087886286</v>
+        <v>-123.998977511332</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>55029</v>
+        <v>55027</v>
       </c>
       <c r="B17">
-        <v>40.0481506989724</v>
+        <v>40.046623419514702</v>
       </c>
       <c r="C17">
-        <v>-123.998977511332</v>
+        <v>-124.045829739881</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -1224,244 +1252,244 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>54027</v>
+        <v>54034</v>
       </c>
       <c r="B19">
-        <v>40.082600017433599</v>
+        <v>40.087870454492503</v>
       </c>
       <c r="C19">
-        <v>-124.04783125889401</v>
+        <v>-123.883759015137</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>54029</v>
+        <v>54033</v>
       </c>
       <c r="B20">
-        <v>40.084128090979704</v>
+        <v>40.087130876124</v>
       </c>
       <c r="C20">
-        <v>-124.000955907376</v>
+        <v>-123.907199355149</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>52522</v>
+        <v>54031</v>
       </c>
       <c r="B21">
-        <v>40.132665553931901</v>
+        <v>40.085638377597903</v>
       </c>
       <c r="C21">
-        <v>-124.168103715577</v>
+        <v>-123.954078598528</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>54031</v>
+        <v>54029</v>
       </c>
       <c r="B22">
-        <v>40.085638377597903</v>
+        <v>40.084128090979704</v>
       </c>
       <c r="C22">
-        <v>-123.954078598528</v>
+        <v>-124.000955907376</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>54033</v>
+        <v>54027</v>
       </c>
       <c r="B23">
-        <v>40.087130876124</v>
+        <v>40.082600017433599</v>
       </c>
       <c r="C23">
-        <v>-123.907199355149</v>
+        <v>-124.04783125889401</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>53525</v>
+        <v>54026</v>
       </c>
       <c r="B24">
-        <v>40.099042388646801</v>
+        <v>40.081829310930203</v>
       </c>
       <c r="C24">
-        <v>-124.09571770071901</v>
+        <v>-124.071268193531</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>54026</v>
+        <v>53525</v>
       </c>
       <c r="B25">
-        <v>40.081829310930203</v>
+        <v>40.099042388646801</v>
       </c>
       <c r="C25">
-        <v>-124.071268193531</v>
+        <v>-124.09571770071901</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>54034</v>
+        <v>53034</v>
       </c>
       <c r="B26">
-        <v>40.087870454492503</v>
+        <v>40.123850689178603</v>
       </c>
       <c r="C26">
-        <v>-123.883759015137</v>
+        <v>-123.885681491471</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>53027</v>
+        <v>53033</v>
       </c>
       <c r="B27">
-        <v>40.1185775079582</v>
+        <v>40.1231107256896</v>
       </c>
       <c r="C27">
-        <v>-124.049834758031</v>
+        <v>-123.909133408318</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>52021</v>
+        <v>53031</v>
       </c>
       <c r="B28">
-        <v>40.149860088443702</v>
+        <v>40.121617450018299</v>
       </c>
       <c r="C28">
-        <v>-124.192593230396</v>
+        <v>-123.956035803235</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>53034</v>
+        <v>53029</v>
       </c>
       <c r="B29">
-        <v>40.123850689178603</v>
+        <v>40.120106377052302</v>
       </c>
       <c r="C29">
-        <v>-123.885681491471</v>
+        <v>-124.00293626075</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>53029</v>
+        <v>53027</v>
       </c>
       <c r="B30">
-        <v>40.120106377052302</v>
+        <v>40.1185775079582</v>
       </c>
       <c r="C30">
-        <v>-124.00293626075</v>
+        <v>-124.049834758031</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>53024</v>
+        <v>53026</v>
       </c>
       <c r="B31">
-        <v>40.1162508391632</v>
+        <v>40.117806400231601</v>
       </c>
       <c r="C31">
-        <v>-124.12017877858</v>
+        <v>-124.073283264449</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>53026</v>
+        <v>53024</v>
       </c>
       <c r="B32">
-        <v>40.117806400231601</v>
+        <v>40.1162508391632</v>
       </c>
       <c r="C32">
-        <v>-124.073283264449</v>
+        <v>-124.12017877858</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>53033</v>
+        <v>52522</v>
       </c>
       <c r="B33">
-        <v>40.1231107256896</v>
+        <v>40.132665553931901</v>
       </c>
       <c r="C33">
-        <v>-123.909133408318</v>
+        <v>-124.168103715577</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>53031</v>
+        <v>52035</v>
       </c>
       <c r="B34">
-        <v>40.121617450018299</v>
+        <v>40.160567734613501</v>
       </c>
       <c r="C34">
-        <v>-123.956035803235</v>
+        <v>-123.864141889352</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>51019</v>
+        <v>52033</v>
       </c>
       <c r="B35">
-        <v>40.184235250018403</v>
+        <v>40.1590914880383</v>
       </c>
       <c r="C35">
-        <v>-124.24160701931299</v>
+        <v>-123.911069376051</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>51520</v>
+        <v>52021</v>
       </c>
       <c r="B36">
-        <v>40.167049987769701</v>
+        <v>40.149860088443702</v>
       </c>
       <c r="C36">
-        <v>-124.21709432999199</v>
+        <v>-124.192593230396</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>51527</v>
+        <v>51531</v>
       </c>
       <c r="B37">
-        <v>40.172545452036999</v>
+        <v>40.1755877723974</v>
       </c>
       <c r="C37">
-        <v>-124.052843725898</v>
+        <v>-123.958975243824</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>50518</v>
+        <v>51529</v>
       </c>
       <c r="B38">
-        <v>40.201415873294401</v>
+        <v>40.174075517196997</v>
       </c>
       <c r="C38">
-        <v>-124.26613130330399</v>
+        <v>-124.005910467162</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>51529</v>
+        <v>51527</v>
       </c>
       <c r="B39">
-        <v>40.174075517196997</v>
+        <v>40.172545452036999</v>
       </c>
       <c r="C39">
-        <v>-124.005910467162</v>
+        <v>-124.052843725898</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>51531</v>
+        <v>51526</v>
       </c>
       <c r="B40">
-        <v>40.1755877723974</v>
+        <v>40.171773741091599</v>
       </c>
       <c r="C40">
-        <v>-123.958975243824</v>
+        <v>-124.07630961139201</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -1488,211 +1516,211 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>52033</v>
+        <v>51520</v>
       </c>
       <c r="B43">
-        <v>40.1590914880383</v>
+        <v>40.167049987769701</v>
       </c>
       <c r="C43">
-        <v>-123.911069376051</v>
+        <v>-124.21709432999199</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>51526</v>
+        <v>51019</v>
       </c>
       <c r="B44">
-        <v>40.171773741091599</v>
+        <v>40.184235250018403</v>
       </c>
       <c r="C44">
-        <v>-124.07630961139201</v>
+        <v>-124.24160701931299</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>52035</v>
+        <v>50535</v>
       </c>
       <c r="B45">
-        <v>40.160567734613501</v>
+        <v>40.214541781029602</v>
       </c>
       <c r="C45">
-        <v>-123.864141889352</v>
+        <v>-123.867014628243</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>49516</v>
+        <v>50533</v>
       </c>
       <c r="B46">
-        <v>40.235763195328502</v>
+        <v>40.213064377770998</v>
       </c>
       <c r="C46">
-        <v>-124.31521467507299</v>
+        <v>-123.913976923677</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>50528</v>
+        <v>50531</v>
       </c>
       <c r="B47">
-        <v>40.209292902947404</v>
+        <v>40.211569152976701</v>
       </c>
       <c r="C47">
-        <v>-124.03137420477</v>
+        <v>-123.960937297432</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>50519</v>
+        <v>50529</v>
       </c>
       <c r="B48">
-        <v>40.202223617880598</v>
+        <v>40.210056107806899</v>
       </c>
       <c r="C48">
-        <v>-124.242657901386</v>
+        <v>-124.007895726583</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>50017</v>
+        <v>50528</v>
       </c>
       <c r="B49">
-        <v>40.218591855698797</v>
+        <v>40.209292902947404</v>
       </c>
       <c r="C49">
-        <v>-124.29066718691</v>
+        <v>-124.03137420477</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>50533</v>
+        <v>50526</v>
       </c>
       <c r="B50">
-        <v>40.213064377770998</v>
+        <v>40.207753129418997</v>
       </c>
       <c r="C50">
-        <v>-123.913976923677</v>
+        <v>-124.078329674049</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>50526</v>
+        <v>50524</v>
       </c>
       <c r="B51">
-        <v>40.207753129418997</v>
+        <v>40.206195538474901</v>
       </c>
       <c r="C51">
-        <v>-124.078329674049</v>
+        <v>-124.125283141441</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>50529</v>
+        <v>50522</v>
       </c>
       <c r="B52">
-        <v>40.210056107806899</v>
+        <v>40.204620131322798</v>
       </c>
       <c r="C52">
-        <v>-124.007895726583</v>
+        <v>-124.172234584045</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>50535</v>
+        <v>50520</v>
       </c>
       <c r="B53">
-        <v>40.214541781029602</v>
+        <v>40.203026909184302</v>
       </c>
       <c r="C53">
-        <v>-123.867014628243</v>
+        <v>-124.21918397896199</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>50520</v>
+        <v>50519</v>
       </c>
       <c r="B54">
-        <v>40.203026909184302</v>
+        <v>40.202223617880598</v>
       </c>
       <c r="C54">
-        <v>-124.21918397896199</v>
+        <v>-124.242657901386</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>50524</v>
+        <v>50518</v>
       </c>
       <c r="B55">
-        <v>40.206195538474901</v>
+        <v>40.201415873294401</v>
       </c>
       <c r="C55">
-        <v>-124.125283141441</v>
+        <v>-124.26613130330399</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>50522</v>
+        <v>50017</v>
       </c>
       <c r="B56">
-        <v>40.204620131322798</v>
+        <v>40.218591855698797</v>
       </c>
       <c r="C56">
-        <v>-124.172234584045</v>
+        <v>-124.29066718691</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>50531</v>
+        <v>49533</v>
       </c>
       <c r="B57">
-        <v>40.211569152976701</v>
+        <v>40.249047491607101</v>
       </c>
       <c r="C57">
-        <v>-123.960937297432</v>
+        <v>-123.915917690268</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>49017</v>
+        <v>49531</v>
       </c>
       <c r="B58">
-        <v>40.254568929307702</v>
+        <v>40.247551484650799</v>
       </c>
       <c r="C58">
-        <v>-124.29279477725601</v>
+        <v>-123.962901295644</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>49522</v>
+        <v>49529</v>
       </c>
       <c r="B59">
-        <v>40.240598828690999</v>
+        <v>40.246037648056898</v>
       </c>
       <c r="C59">
-        <v>-124.17430308829</v>
+        <v>-124.009882953526</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>49015</v>
+        <v>49528</v>
       </c>
       <c r="B60">
-        <v>40.252929890276803</v>
+        <v>40.245274044012902</v>
       </c>
       <c r="C60">
-        <v>-124.339773772735</v>
+        <v>-124.033373044984</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>49533</v>
+        <v>49526</v>
       </c>
       <c r="B61">
-        <v>40.249047491607101</v>
+        <v>40.243733465172902</v>
       </c>
       <c r="C61">
-        <v>-123.915917690268</v>
+        <v>-124.080351738593</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -1708,332 +1736,332 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>49019</v>
+        <v>49522</v>
       </c>
       <c r="B63">
-        <v>40.256190142595898</v>
+        <v>40.240598828690999</v>
       </c>
       <c r="C63">
-        <v>-124.245813672182</v>
+        <v>-124.17430308829</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>49531</v>
+        <v>49516</v>
       </c>
       <c r="B64">
-        <v>40.247551484650799</v>
+        <v>40.235763195328502</v>
       </c>
       <c r="C64">
-        <v>-123.962901295644</v>
+        <v>-124.31521467507299</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>49528</v>
+        <v>49021</v>
       </c>
       <c r="B65">
-        <v>40.245274044012902</v>
+        <v>40.257793528881599</v>
       </c>
       <c r="C65">
-        <v>-124.033373044984</v>
+        <v>-124.198830480445</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>49021</v>
+        <v>49019</v>
       </c>
       <c r="B66">
-        <v>40.257793528881599</v>
+        <v>40.256190142595898</v>
       </c>
       <c r="C66">
-        <v>-124.198830480445</v>
+        <v>-124.245813672182</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>49529</v>
+        <v>49017</v>
       </c>
       <c r="B67">
-        <v>40.246037648056898</v>
+        <v>40.254568929307702</v>
       </c>
       <c r="C67">
-        <v>-124.009882953526</v>
+        <v>-124.29279477725601</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>49526</v>
+        <v>49015</v>
       </c>
       <c r="B68">
-        <v>40.243733465172902</v>
+        <v>40.252929890276803</v>
       </c>
       <c r="C68">
-        <v>-124.080351738593</v>
+        <v>-124.339773772735</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>48024</v>
+        <v>48531</v>
       </c>
       <c r="B69">
-        <v>40.2961461499264</v>
+        <v>40.283534783366498</v>
       </c>
       <c r="C69">
-        <v>-124.13040015925399</v>
+        <v>-123.964867241351</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>48028</v>
+        <v>48030</v>
       </c>
       <c r="B70">
-        <v>40.2992475696919</v>
+        <v>40.300771517495797</v>
       </c>
       <c r="C70">
-        <v>-124.03637502232399</v>
+        <v>-123.989359462849</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>48015</v>
+        <v>48028</v>
       </c>
       <c r="B71">
-        <v>40.288907069792401</v>
+        <v>40.2992475696919</v>
       </c>
       <c r="C71">
-        <v>-124.341926714601</v>
+        <v>-124.03637502232399</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>48030</v>
+        <v>48026</v>
       </c>
       <c r="B72">
-        <v>40.300771517495797</v>
+        <v>40.297705780101701</v>
       </c>
       <c r="C72">
-        <v>-123.989359462849</v>
+        <v>-124.083388595457</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>48017</v>
+        <v>48024</v>
       </c>
       <c r="B73">
-        <v>40.290546967368599</v>
+        <v>40.2961461499264</v>
       </c>
       <c r="C73">
-        <v>-124.29492447719799</v>
+        <v>-124.13040015925399</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>48531</v>
+        <v>48022</v>
       </c>
       <c r="B74">
-        <v>40.283534783366498</v>
+        <v>40.294568680380799</v>
       </c>
       <c r="C74">
-        <v>-123.964867241351</v>
+        <v>-124.17740969072899</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>48019</v>
+        <v>48021</v>
       </c>
       <c r="B75">
-        <v>40.292169029934598</v>
+        <v>40.293773256227603</v>
       </c>
       <c r="C75">
-        <v>-124.24792012706401</v>
+        <v>-124.20091368716299</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>48022</v>
+        <v>48019</v>
       </c>
       <c r="B76">
-        <v>40.294568680380799</v>
+        <v>40.292169029934598</v>
       </c>
       <c r="C76">
-        <v>-124.17740969072899</v>
+        <v>-124.24792012706401</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>48021</v>
+        <v>48017</v>
       </c>
       <c r="B77">
-        <v>40.293773256227603</v>
+        <v>40.290546967368599</v>
       </c>
       <c r="C77">
-        <v>-124.20091368716299</v>
+        <v>-124.29492447719799</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>48026</v>
+        <v>48015</v>
       </c>
       <c r="B78">
-        <v>40.297705780101701</v>
+        <v>40.288907069792401</v>
       </c>
       <c r="C78">
-        <v>-124.083388595457</v>
+        <v>-124.341926714601</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>47023</v>
+        <v>47030</v>
       </c>
       <c r="B79">
-        <v>40.331341188141003</v>
+        <v>40.336755900363599</v>
       </c>
       <c r="C79">
-        <v>-124.15596717976899</v>
+        <v>-123.99133997868201</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>47015</v>
+        <v>47028</v>
       </c>
       <c r="B80">
-        <v>40.324885228143799</v>
+        <v>40.335231152833302</v>
       </c>
       <c r="C80">
-        <v>-124.34408179216101</v>
+        <v>-124.038378822864</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>47019</v>
+        <v>47026</v>
       </c>
       <c r="B81">
-        <v>40.328148899256398</v>
+        <v>40.333688554216302</v>
       </c>
       <c r="C81">
-        <v>-124.250028671712</v>
+        <v>-124.085415677748</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>46515</v>
+        <v>47024</v>
       </c>
       <c r="B82">
-        <v>40.3428746793792</v>
+        <v>40.332128105716698</v>
       </c>
       <c r="C82">
-        <v>-124.34516013281799</v>
+        <v>-124.132450520307</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>47024</v>
+        <v>47023</v>
       </c>
       <c r="B83">
-        <v>40.332128105716698</v>
+        <v>40.331341188141003</v>
       </c>
       <c r="C83">
-        <v>-124.132450520307</v>
+        <v>-124.15596717976899</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>47017</v>
+        <v>47021</v>
       </c>
       <c r="B84">
-        <v>40.326525985847503</v>
+        <v>40.329753967104999</v>
       </c>
       <c r="C84">
-        <v>-124.29705628987401</v>
+        <v>-124.202998960675</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>47021</v>
+        <v>47019</v>
       </c>
       <c r="B85">
-        <v>40.329753967104999</v>
+        <v>40.328148899256398</v>
       </c>
       <c r="C85">
-        <v>-124.202998960675</v>
+        <v>-124.250028671712</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>47026</v>
+        <v>47017</v>
       </c>
       <c r="B86">
-        <v>40.333688554216302</v>
+        <v>40.326525985847503</v>
       </c>
       <c r="C86">
-        <v>-124.085415677748</v>
+        <v>-124.29705628987401</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>47028</v>
+        <v>47015</v>
       </c>
       <c r="B87">
-        <v>40.335231152833302</v>
+        <v>40.324885228143799</v>
       </c>
       <c r="C87">
-        <v>-124.038378822864</v>
+        <v>-124.34408179216101</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>47030</v>
+        <v>46515</v>
       </c>
       <c r="B88">
-        <v>40.336755900363599</v>
+        <v>40.3428746793792</v>
       </c>
       <c r="C88">
-        <v>-123.99133997868201</v>
+        <v>-124.34516013281799</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>45519</v>
+        <v>46030</v>
       </c>
       <c r="B89">
-        <v>40.382120579463397</v>
+        <v>40.372741289537402</v>
       </c>
       <c r="C89">
-        <v>-124.253195413802</v>
+        <v>-123.993322460781</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B90">
-        <v>40.368111063336698</v>
+        <v>40.371215740805603</v>
       </c>
       <c r="C90">
-        <v>-124.13450291670701</v>
+        <v>-124.040384612704</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>46030</v>
+        <v>46026</v>
       </c>
       <c r="B91">
-        <v>40.372741289537402</v>
+        <v>40.369672331669697</v>
       </c>
       <c r="C91">
-        <v>-123.993322460781</v>
+        <v>-124.08744477236699</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>45517</v>
+        <v>46024</v>
       </c>
       <c r="B92">
-        <v>40.380496386847298</v>
+        <v>40.368111063336698</v>
       </c>
       <c r="C92">
-        <v>-124.300257977141</v>
+        <v>-124.13450291670701</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -2049,35 +2077,35 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>46026</v>
+        <v>45521</v>
       </c>
       <c r="B94">
-        <v>40.369672331669697</v>
+        <v>40.3837269125559</v>
       </c>
       <c r="C94">
-        <v>-124.08744477236699</v>
+        <v>-124.206130752912</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>46028</v>
+        <v>45519</v>
       </c>
       <c r="B95">
-        <v>40.371215740805603</v>
+        <v>40.382120579463397</v>
       </c>
       <c r="C95">
-        <v>-124.040384612704</v>
+        <v>-124.253195413802</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>45521</v>
+        <v>45517</v>
       </c>
       <c r="B96">
-        <v>40.3837269125559</v>
+        <v>40.380496386847298</v>
       </c>
       <c r="C96">
-        <v>-124.206130752912</v>
+        <v>-124.300257977141</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -2093,101 +2121,101 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>45014</v>
+        <v>45030</v>
       </c>
       <c r="B98">
-        <v>40.3960166057986</v>
+        <v>40.408727701064898</v>
       </c>
       <c r="C98">
-        <v>-124.371933614586</v>
+        <v>-123.995306912074</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>44521</v>
+        <v>45014</v>
       </c>
       <c r="B99">
-        <v>40.419710152337501</v>
+        <v>40.3960166057986</v>
       </c>
       <c r="C99">
-        <v>-124.20822120687799</v>
+        <v>-124.371933614586</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>44523</v>
+        <v>44528</v>
       </c>
       <c r="B100">
-        <v>40.421299460758803</v>
+        <v>40.425194541927198</v>
       </c>
       <c r="C100">
-        <v>-124.161131139688</v>
+        <v>-124.04339703388</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="B101">
-        <v>40.422870897821497</v>
+        <v>40.4236499142078</v>
       </c>
       <c r="C101">
-        <v>-124.114039018013</v>
+        <v>-124.09049219396201</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>44526</v>
+        <v>44525</v>
       </c>
       <c r="B102">
-        <v>40.4236499142078</v>
+        <v>40.422870897821497</v>
       </c>
       <c r="C102">
-        <v>-124.09049219396201</v>
+        <v>-124.114039018013</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>44528</v>
+        <v>44523</v>
       </c>
       <c r="B103">
-        <v>40.425194541927198</v>
+        <v>40.421299460758803</v>
       </c>
       <c r="C103">
-        <v>-124.04339703388</v>
+        <v>-124.161131139688</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>45030</v>
+        <v>44521</v>
       </c>
       <c r="B104">
-        <v>40.408727701064898</v>
+        <v>40.419710152337501</v>
       </c>
       <c r="C104">
-        <v>-123.995306912074</v>
+        <v>-124.20822120687799</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>44013</v>
+        <v>44519</v>
       </c>
       <c r="B105">
-        <v>40.431164517699301</v>
+        <v>40.418102973803201</v>
       </c>
       <c r="C105">
-        <v>-124.397653157405</v>
+        <v>-124.255309196485</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>44514</v>
+        <v>44517</v>
       </c>
       <c r="B106">
-        <v>40.4140068540217</v>
+        <v>40.416477926415297</v>
       </c>
       <c r="C106">
-        <v>-124.37301992954799</v>
+        <v>-124.30239508541599</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
@@ -2203,24 +2231,24 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>44517</v>
+        <v>44514</v>
       </c>
       <c r="B108">
-        <v>40.416477926415297</v>
+        <v>40.4140068540217</v>
       </c>
       <c r="C108">
-        <v>-124.30239508541599</v>
+        <v>-124.37301992954799</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>44519</v>
+        <v>44013</v>
       </c>
       <c r="B109">
-        <v>40.418102973803201</v>
+        <v>40.431164517699301</v>
       </c>
       <c r="C109">
-        <v>-124.255309196485</v>
+        <v>-124.397653157405</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
@@ -2236,24 +2264,24 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>43513</v>
+        <v>43526</v>
       </c>
       <c r="B111">
-        <v>40.449155065554301</v>
+        <v>40.459636270252197</v>
       </c>
       <c r="C111">
-        <v>-124.398746388777</v>
+        <v>-124.092526332519</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>43521</v>
+        <v>43525</v>
       </c>
       <c r="B112">
-        <v>40.4556944317887</v>
+        <v>40.458856843224602</v>
       </c>
       <c r="C112">
-        <v>-124.21031373842899</v>
+        <v>-124.11608483669001</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
@@ -2269,156 +2297,156 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>43514</v>
+        <v>43521</v>
       </c>
       <c r="B114">
-        <v>40.449988128075901</v>
+        <v>40.4556944317887</v>
       </c>
       <c r="C114">
-        <v>-124.37519417865499</v>
+        <v>-124.21031373842899</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>43516</v>
+        <v>43519</v>
       </c>
       <c r="B115">
-        <v>40.451640846717801</v>
+        <v>40.454086406251697</v>
       </c>
       <c r="C115">
-        <v>-124.328088140104</v>
+        <v>-124.257425079844</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>43525</v>
+        <v>43518</v>
       </c>
       <c r="B116">
-        <v>40.458856843224602</v>
+        <v>40.453275689078403</v>
       </c>
       <c r="C116">
-        <v>-124.11608483669001</v>
+        <v>-124.280979963069</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>43518</v>
+        <v>43516</v>
       </c>
       <c r="B117">
-        <v>40.453275689078403</v>
+        <v>40.451640846717801</v>
       </c>
       <c r="C117">
-        <v>-124.280979963069</v>
+        <v>-124.328088140104</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>43526</v>
+        <v>43514</v>
       </c>
       <c r="B118">
-        <v>40.459636270252197</v>
+        <v>40.449988128075901</v>
       </c>
       <c r="C118">
-        <v>-124.092526332519</v>
+        <v>-124.37519417865499</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>43519</v>
+        <v>43513</v>
       </c>
       <c r="B119">
-        <v>40.454086406251697</v>
+        <v>40.449155065554301</v>
       </c>
       <c r="C119">
-        <v>-124.257425079844</v>
+        <v>-124.398746388777</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>42014</v>
+        <v>42525</v>
       </c>
       <c r="B120">
-        <v>40.503962013366099</v>
+        <v>40.494843847481</v>
       </c>
       <c r="C120">
-        <v>-124.378459606315</v>
+        <v>-124.118132689779</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>42019</v>
+        <v>42523</v>
       </c>
       <c r="B121">
-        <v>40.508063536610898</v>
+        <v>40.493270752289398</v>
       </c>
       <c r="C121">
-        <v>-124.260602850502</v>
+        <v>-124.165271550528</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>42525</v>
+        <v>42521</v>
       </c>
       <c r="B122">
-        <v>40.494843847481</v>
+        <v>40.491679767015697</v>
       </c>
       <c r="C122">
-        <v>-124.118132689779</v>
+        <v>-124.21240835066099</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>42016</v>
+        <v>42019</v>
       </c>
       <c r="B123">
-        <v>40.505616040570899</v>
+        <v>40.508063536610898</v>
       </c>
       <c r="C123">
-        <v>-124.331318508546</v>
+        <v>-124.260602850502</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>42521</v>
+        <v>42018</v>
       </c>
       <c r="B124">
-        <v>40.491679767015697</v>
+        <v>40.507252177448102</v>
       </c>
       <c r="C124">
-        <v>-124.21240835066099</v>
+        <v>-124.284175267507</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>42523</v>
+        <v>42016</v>
       </c>
       <c r="B125">
-        <v>40.493270752289398</v>
+        <v>40.505616040570899</v>
       </c>
       <c r="C125">
-        <v>-124.165271550528</v>
+        <v>-124.331318508546</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>42018</v>
+        <v>42014</v>
       </c>
       <c r="B126">
-        <v>40.507252177448102</v>
+        <v>40.503962013366099</v>
       </c>
       <c r="C126">
-        <v>-124.284175267507</v>
+        <v>-124.378459606315</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>41015</v>
+        <v>41021</v>
       </c>
       <c r="B127">
-        <v>40.540775631403399</v>
+        <v>40.545659784742099</v>
       </c>
       <c r="C127">
-        <v>-124.35705728545101</v>
+        <v>-124.21555417707501</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
@@ -2434,35 +2462,35 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>41016</v>
+        <v>41018</v>
       </c>
       <c r="B129">
-        <v>40.541600844818298</v>
+        <v>40.543237846700599</v>
       </c>
       <c r="C129">
-        <v>-124.333474765929</v>
+        <v>-124.286308119935</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>41018</v>
+        <v>41016</v>
       </c>
       <c r="B130">
-        <v>40.543237846700599</v>
+        <v>40.541600844818298</v>
       </c>
       <c r="C130">
-        <v>-124.286308119935</v>
+        <v>-124.333474765929</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>41021</v>
+        <v>41015</v>
       </c>
       <c r="B131">
-        <v>40.545659784742099</v>
+        <v>40.540775631403399</v>
       </c>
       <c r="C131">
-        <v>-124.21555417707501</v>
+        <v>-124.35705728545101</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
@@ -2478,57 +2506,57 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133">
-        <v>40018</v>
+        <v>40020</v>
       </c>
       <c r="B133">
-        <v>40.579224609758697</v>
+        <v>40.580844567836003</v>
       </c>
       <c r="C133">
-        <v>-124.28844309562901</v>
+        <v>-124.241250895042</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>40016</v>
+        <v>40018</v>
       </c>
       <c r="B134">
-        <v>40.577586741271503</v>
+        <v>40.579224609758697</v>
       </c>
       <c r="C134">
-        <v>-124.335633169781</v>
+        <v>-124.28844309562901</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>40020</v>
+        <v>40016</v>
       </c>
       <c r="B135">
-        <v>40.580844567836003</v>
+        <v>40.577586741271503</v>
       </c>
       <c r="C135">
-        <v>-124.241250895042</v>
+        <v>-124.335633169781</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136">
-        <v>38517</v>
+        <v>38518</v>
       </c>
       <c r="B136">
-        <v>40.632389495477298</v>
+        <v>40.633206840690299</v>
       </c>
       <c r="C136">
-        <v>-124.315262445068</v>
+        <v>-124.291649547228</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>38518</v>
+        <v>38517</v>
       </c>
       <c r="B137">
-        <v>40.633206840690299</v>
+        <v>40.632389495477298</v>
       </c>
       <c r="C137">
-        <v>-124.291649547228</v>
+        <v>-124.315262445068</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
@@ -2543,6 +2571,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C138">
+    <sortCondition descending="1" ref="A1:A138"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2568,1971 +2599,1971 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>314741</v>
+        <v>311927</v>
       </c>
       <c r="B2">
-        <v>40.583333330000002</v>
+        <v>40.666666666658898</v>
       </c>
       <c r="C2">
-        <v>-124.16666669999999</v>
+        <v>-124.33333333333201</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>314742</v>
+        <v>311928</v>
       </c>
       <c r="B3">
-        <v>40.583333330000002</v>
+        <v>40.666666666658898</v>
       </c>
       <c r="C3">
-        <v>-124.125</v>
+        <v>-124.291666666666</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>316144</v>
+        <v>313332</v>
       </c>
       <c r="B4">
-        <v>40.541666669999998</v>
+        <v>40.624999999992198</v>
       </c>
       <c r="C4">
-        <v>-124.25</v>
+        <v>-124.33333333333201</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>316145</v>
+        <v>313333</v>
       </c>
       <c r="B5">
-        <v>40.541666669999998</v>
+        <v>40.624999999992198</v>
       </c>
       <c r="C5">
-        <v>-124.20833330000001</v>
+        <v>-124.291666666666</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>316146</v>
+        <v>314736</v>
       </c>
       <c r="B6">
-        <v>40.541666669999998</v>
+        <v>40.583333333325498</v>
       </c>
       <c r="C6">
-        <v>-124.16666669999999</v>
+        <v>-124.37499999999901</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>316147</v>
+        <v>314737</v>
       </c>
       <c r="B7">
-        <v>40.541666669999998</v>
+        <v>40.583333333325498</v>
       </c>
       <c r="C7">
-        <v>-124.125</v>
+        <v>-124.33333333333201</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>316148</v>
+        <v>314738</v>
       </c>
       <c r="B8">
-        <v>40.541666669999998</v>
+        <v>40.583333333325498</v>
       </c>
       <c r="C8">
-        <v>-124.08333330000001</v>
+        <v>-124.291666666666</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>316149</v>
+        <v>314739</v>
       </c>
       <c r="B9">
-        <v>40.541666669999998</v>
+        <v>40.583333333325498</v>
       </c>
       <c r="C9">
-        <v>-124.04166669999999</v>
+        <v>-124.24999999999901</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>316150</v>
+        <v>314741</v>
       </c>
       <c r="B10">
-        <v>40.541666669999998</v>
+        <v>40.583333330000002</v>
       </c>
       <c r="C10">
-        <v>-124</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>317547</v>
+        <v>314742</v>
       </c>
       <c r="B11">
-        <v>40.5</v>
+        <v>40.583333330000002</v>
       </c>
       <c r="C11">
-        <v>-124.33333330000001</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>317548</v>
+        <v>316141</v>
       </c>
       <c r="B12">
-        <v>40.5</v>
+        <v>40.541666666658799</v>
       </c>
       <c r="C12">
-        <v>-124.29166669999999</v>
+        <v>-124.37499999999901</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>317549</v>
+        <v>316142</v>
       </c>
       <c r="B13">
-        <v>40.5</v>
+        <v>40.541666666658799</v>
       </c>
       <c r="C13">
-        <v>-124.25</v>
+        <v>-124.33333333333201</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>317550</v>
+        <v>316143</v>
       </c>
       <c r="B14">
-        <v>40.5</v>
+        <v>40.541666666658799</v>
       </c>
       <c r="C14">
-        <v>-124.20833330000001</v>
+        <v>-124.291666666666</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>317551</v>
+        <v>316144</v>
       </c>
       <c r="B15">
-        <v>40.5</v>
+        <v>40.541666669999998</v>
       </c>
       <c r="C15">
-        <v>-124.16666669999999</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>317552</v>
+        <v>316145</v>
       </c>
       <c r="B16">
-        <v>40.5</v>
+        <v>40.541666669999998</v>
       </c>
       <c r="C16">
-        <v>-124.125</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>317553</v>
+        <v>316146</v>
       </c>
       <c r="B17">
-        <v>40.5</v>
+        <v>40.541666669999998</v>
       </c>
       <c r="C17">
-        <v>-124.08333330000001</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>317554</v>
+        <v>316147</v>
       </c>
       <c r="B18">
-        <v>40.5</v>
+        <v>40.541666669999998</v>
       </c>
       <c r="C18">
-        <v>-124.04166669999999</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>317555</v>
+        <v>316148</v>
       </c>
       <c r="B19">
-        <v>40.5</v>
+        <v>40.541666669999998</v>
       </c>
       <c r="C19">
-        <v>-124</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>317556</v>
+        <v>316149</v>
       </c>
       <c r="B20">
-        <v>40.5</v>
+        <v>40.541666669999998</v>
       </c>
       <c r="C20">
-        <v>-123.95833330000001</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>317557</v>
+        <v>316150</v>
       </c>
       <c r="B21">
-        <v>40.5</v>
+        <v>40.541666669999998</v>
       </c>
       <c r="C21">
-        <v>-123.91666669999999</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>318951</v>
+        <v>317545</v>
       </c>
       <c r="B22">
-        <v>40.458333330000002</v>
+        <v>40.499999999992099</v>
       </c>
       <c r="C22">
-        <v>-124.375</v>
+        <v>-124.416666666666</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>318952</v>
+        <v>317546</v>
       </c>
       <c r="B23">
-        <v>40.458333330000002</v>
+        <v>40.499999999992099</v>
       </c>
       <c r="C23">
-        <v>-124.33333330000001</v>
+        <v>-124.37499999999901</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>318953</v>
+        <v>317547</v>
       </c>
       <c r="B24">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C24">
-        <v>-124.29166669999999</v>
+        <v>-124.33333330000001</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>318954</v>
+        <v>317548</v>
       </c>
       <c r="B25">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C25">
-        <v>-124.25</v>
+        <v>-124.29166669999999</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>318955</v>
+        <v>317549</v>
       </c>
       <c r="B26">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C26">
-        <v>-124.20833330000001</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>318956</v>
+        <v>317550</v>
       </c>
       <c r="B27">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C27">
-        <v>-124.16666669999999</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>318957</v>
+        <v>317551</v>
       </c>
       <c r="B28">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C28">
-        <v>-124.125</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>318958</v>
+        <v>317552</v>
       </c>
       <c r="B29">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C29">
-        <v>-124.08333330000001</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>318959</v>
+        <v>317553</v>
       </c>
       <c r="B30">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C30">
-        <v>-124.04166669999999</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>318960</v>
+        <v>317554</v>
       </c>
       <c r="B31">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C31">
-        <v>-124</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>318961</v>
+        <v>317555</v>
       </c>
       <c r="B32">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C32">
-        <v>-123.95833330000001</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>318962</v>
+        <v>317556</v>
       </c>
       <c r="B33">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C33">
-        <v>-123.91666669999999</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>318963</v>
+        <v>317557</v>
       </c>
       <c r="B34">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C34">
-        <v>-123.875</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>320356</v>
+        <v>318950</v>
       </c>
       <c r="B35">
-        <v>40.416666669999998</v>
+        <v>40.458333333325399</v>
       </c>
       <c r="C35">
-        <v>-124.375</v>
+        <v>-124.416666666666</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>320357</v>
+        <v>318951</v>
       </c>
       <c r="B36">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C36">
-        <v>-124.33333330000001</v>
+        <v>-124.375</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>320358</v>
+        <v>318952</v>
       </c>
       <c r="B37">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C37">
-        <v>-124.29166669999999</v>
+        <v>-124.33333330000001</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>320359</v>
+        <v>318953</v>
       </c>
       <c r="B38">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C38">
-        <v>-124.25</v>
+        <v>-124.29166669999999</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>320360</v>
+        <v>318954</v>
       </c>
       <c r="B39">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C39">
-        <v>-124.20833330000001</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>320361</v>
+        <v>318955</v>
       </c>
       <c r="B40">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C40">
-        <v>-124.16666669999999</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>320362</v>
+        <v>318956</v>
       </c>
       <c r="B41">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C41">
-        <v>-124.125</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>320363</v>
+        <v>318957</v>
       </c>
       <c r="B42">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C42">
-        <v>-124.08333330000001</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>320364</v>
+        <v>318958</v>
       </c>
       <c r="B43">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C43">
-        <v>-124.04166669999999</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>320365</v>
+        <v>318959</v>
       </c>
       <c r="B44">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C44">
-        <v>-124</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>320366</v>
+        <v>318960</v>
       </c>
       <c r="B45">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C45">
-        <v>-123.95833330000001</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>320367</v>
+        <v>318961</v>
       </c>
       <c r="B46">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C46">
-        <v>-123.91666669999999</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>320368</v>
+        <v>318962</v>
       </c>
       <c r="B47">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C47">
-        <v>-123.875</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>321762</v>
+        <v>318963</v>
       </c>
       <c r="B48">
-        <v>40.375</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C48">
-        <v>-124.33333330000001</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>321763</v>
+        <v>320355</v>
       </c>
       <c r="B49">
-        <v>40.375</v>
+        <v>40.416666666658699</v>
       </c>
       <c r="C49">
-        <v>-124.29166669999999</v>
+        <v>-124.416666666666</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>321764</v>
+        <v>320356</v>
       </c>
       <c r="B50">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C50">
-        <v>-124.25</v>
+        <v>-124.375</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>321765</v>
+        <v>320357</v>
       </c>
       <c r="B51">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C51">
-        <v>-124.20833330000001</v>
+        <v>-124.33333330000001</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>321766</v>
+        <v>320358</v>
       </c>
       <c r="B52">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C52">
-        <v>-124.16666669999999</v>
+        <v>-124.29166669999999</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>321767</v>
+        <v>320359</v>
       </c>
       <c r="B53">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C53">
-        <v>-124.125</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>321768</v>
+        <v>320360</v>
       </c>
       <c r="B54">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C54">
-        <v>-124.08333330000001</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>321769</v>
+        <v>320361</v>
       </c>
       <c r="B55">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C55">
-        <v>-124.04166669999999</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>321770</v>
+        <v>320362</v>
       </c>
       <c r="B56">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C56">
-        <v>-124</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>321771</v>
+        <v>320363</v>
       </c>
       <c r="B57">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C57">
-        <v>-123.95833330000001</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>321772</v>
+        <v>320364</v>
       </c>
       <c r="B58">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C58">
-        <v>-123.91666669999999</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>321773</v>
+        <v>320365</v>
       </c>
       <c r="B59">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C59">
-        <v>-123.875</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>323167</v>
+        <v>320366</v>
       </c>
       <c r="B60">
-        <v>40.333333330000002</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C60">
-        <v>-124.33333330000001</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>323168</v>
+        <v>320367</v>
       </c>
       <c r="B61">
-        <v>40.333333330000002</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C61">
-        <v>-124.29166669999999</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>323169</v>
+        <v>320368</v>
       </c>
       <c r="B62">
-        <v>40.333333330000002</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C62">
-        <v>-124.25</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>323170</v>
+        <v>321761</v>
       </c>
       <c r="B63">
-        <v>40.333333330000002</v>
+        <v>40.374999999991999</v>
       </c>
       <c r="C63">
-        <v>-124.20833330000001</v>
+        <v>-124.37499999999901</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>323171</v>
+        <v>321762</v>
       </c>
       <c r="B64">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C64">
-        <v>-124.16666669999999</v>
+        <v>-124.33333330000001</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>323172</v>
+        <v>321763</v>
       </c>
       <c r="B65">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C65">
-        <v>-124.125</v>
+        <v>-124.29166669999999</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>323173</v>
+        <v>321764</v>
       </c>
       <c r="B66">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C66">
-        <v>-124.08333330000001</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>323174</v>
+        <v>321765</v>
       </c>
       <c r="B67">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C67">
-        <v>-124.04166669999999</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>323175</v>
+        <v>321766</v>
       </c>
       <c r="B68">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C68">
-        <v>-124</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>323176</v>
+        <v>321767</v>
       </c>
       <c r="B69">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C69">
-        <v>-123.95833330000001</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>323177</v>
+        <v>321768</v>
       </c>
       <c r="B70">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C70">
-        <v>-123.91666669999999</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>323178</v>
+        <v>321769</v>
       </c>
       <c r="B71">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C71">
-        <v>-123.875</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>323179</v>
+        <v>321770</v>
       </c>
       <c r="B72">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C72">
-        <v>-123.83333330000001</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>324572</v>
+        <v>321771</v>
       </c>
       <c r="B73">
-        <v>40.291666669999998</v>
+        <v>40.375</v>
       </c>
       <c r="C73">
-        <v>-124.33333330000001</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>324573</v>
+        <v>321772</v>
       </c>
       <c r="B74">
-        <v>40.291666669999998</v>
+        <v>40.375</v>
       </c>
       <c r="C74">
-        <v>-124.29166669999999</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>324574</v>
+        <v>321773</v>
       </c>
       <c r="B75">
-        <v>40.291666669999998</v>
+        <v>40.375</v>
       </c>
       <c r="C75">
-        <v>-124.25</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>324575</v>
+        <v>323166</v>
       </c>
       <c r="B76">
-        <v>40.291666669999998</v>
+        <v>40.333333333325299</v>
       </c>
       <c r="C76">
-        <v>-124.20833330000001</v>
+        <v>-124.37499999999901</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>324576</v>
+        <v>323167</v>
       </c>
       <c r="B77">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C77">
-        <v>-124.16666669999999</v>
+        <v>-124.33333330000001</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>324577</v>
+        <v>323168</v>
       </c>
       <c r="B78">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C78">
-        <v>-124.125</v>
+        <v>-124.29166669999999</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>324578</v>
+        <v>323169</v>
       </c>
       <c r="B79">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C79">
-        <v>-124.08333330000001</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>324579</v>
+        <v>323170</v>
       </c>
       <c r="B80">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C80">
-        <v>-124.04166669999999</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>324580</v>
+        <v>323171</v>
       </c>
       <c r="B81">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C81">
-        <v>-124</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>324581</v>
+        <v>323172</v>
       </c>
       <c r="B82">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C82">
-        <v>-123.95833330000001</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>324582</v>
+        <v>323173</v>
       </c>
       <c r="B83">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C83">
-        <v>-123.91666669999999</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>324583</v>
+        <v>323174</v>
       </c>
       <c r="B84">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C84">
-        <v>-123.875</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>324584</v>
+        <v>323175</v>
       </c>
       <c r="B85">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C85">
-        <v>-123.83333330000001</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>324585</v>
+        <v>323176</v>
       </c>
       <c r="B86">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C86">
-        <v>-123.79166669999999</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>325977</v>
+        <v>323177</v>
       </c>
       <c r="B87">
-        <v>40.25</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C87">
-        <v>-124.33333330000001</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>325978</v>
+        <v>323178</v>
       </c>
       <c r="B88">
-        <v>40.25</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C88">
-        <v>-124.29166669999999</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>325979</v>
+        <v>323179</v>
       </c>
       <c r="B89">
-        <v>40.25</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C89">
-        <v>-124.25</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>325980</v>
+        <v>324571</v>
       </c>
       <c r="B90">
-        <v>40.25</v>
+        <v>40.2916666666586</v>
       </c>
       <c r="C90">
-        <v>-124.20833330000001</v>
+        <v>-124.37499999999901</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>325981</v>
+        <v>324572</v>
       </c>
       <c r="B91">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C91">
-        <v>-124.16666669999999</v>
+        <v>-124.33333330000001</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>325982</v>
+        <v>324573</v>
       </c>
       <c r="B92">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C92">
-        <v>-124.125</v>
+        <v>-124.29166669999999</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>325983</v>
+        <v>324574</v>
       </c>
       <c r="B93">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C93">
-        <v>-124.08333330000001</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>325984</v>
+        <v>324575</v>
       </c>
       <c r="B94">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C94">
-        <v>-124.04166669999999</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>325985</v>
+        <v>324576</v>
       </c>
       <c r="B95">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C95">
-        <v>-124</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>325986</v>
+        <v>324577</v>
       </c>
       <c r="B96">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C96">
-        <v>-123.95833330000001</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>325987</v>
+        <v>324578</v>
       </c>
       <c r="B97">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C97">
-        <v>-123.91666669999999</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>325988</v>
+        <v>324579</v>
       </c>
       <c r="B98">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C98">
-        <v>-123.875</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>325989</v>
+        <v>324580</v>
       </c>
       <c r="B99">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C99">
-        <v>-123.83333330000001</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>325990</v>
+        <v>324581</v>
       </c>
       <c r="B100">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C100">
-        <v>-123.79166669999999</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>327383</v>
+        <v>324582</v>
       </c>
       <c r="B101">
-        <v>40.208333330000002</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C101">
-        <v>-124.29166669999999</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>327384</v>
+        <v>324583</v>
       </c>
       <c r="B102">
-        <v>40.208333330000002</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C102">
-        <v>-124.25</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>327385</v>
+        <v>324584</v>
       </c>
       <c r="B103">
-        <v>40.208333330000002</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C103">
-        <v>-124.20833330000001</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>327386</v>
+        <v>324585</v>
       </c>
       <c r="B104">
-        <v>40.208333330000002</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C104">
-        <v>-124.16666669999999</v>
+        <v>-123.79166669999999</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>327387</v>
+        <v>325976</v>
       </c>
       <c r="B105">
-        <v>40.208333330000002</v>
+        <v>40.2499999999919</v>
       </c>
       <c r="C105">
-        <v>-124.125</v>
+        <v>-124.37499999999901</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>327388</v>
+        <v>325977</v>
       </c>
       <c r="B106">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C106">
-        <v>-124.08333330000001</v>
+        <v>-124.33333330000001</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>327389</v>
+        <v>325978</v>
       </c>
       <c r="B107">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C107">
-        <v>-124.04166669999999</v>
+        <v>-124.29166669999999</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>327390</v>
+        <v>325979</v>
       </c>
       <c r="B108">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C108">
-        <v>-124</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>327391</v>
+        <v>325980</v>
       </c>
       <c r="B109">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C109">
-        <v>-123.95833330000001</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>327392</v>
+        <v>325981</v>
       </c>
       <c r="B110">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C110">
-        <v>-123.91666669999999</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>327393</v>
+        <v>325982</v>
       </c>
       <c r="B111">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C111">
-        <v>-123.875</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>327394</v>
+        <v>325983</v>
       </c>
       <c r="B112">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C112">
-        <v>-123.83333330000001</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>327395</v>
+        <v>325984</v>
       </c>
       <c r="B113">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C113">
-        <v>-123.79166669999999</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>327396</v>
+        <v>325985</v>
       </c>
       <c r="B114">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C114">
-        <v>-123.75</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>328790</v>
+        <v>325986</v>
       </c>
       <c r="B115">
-        <v>40.166666669999998</v>
+        <v>40.25</v>
       </c>
       <c r="C115">
-        <v>-124.20833330000001</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>328791</v>
+        <v>325987</v>
       </c>
       <c r="B116">
-        <v>40.166666669999998</v>
+        <v>40.25</v>
       </c>
       <c r="C116">
-        <v>-124.16666669999999</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>328792</v>
+        <v>325988</v>
       </c>
       <c r="B117">
-        <v>40.166666669999998</v>
+        <v>40.25</v>
       </c>
       <c r="C117">
-        <v>-124.125</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>328793</v>
+        <v>325989</v>
       </c>
       <c r="B118">
-        <v>40.166666669999998</v>
+        <v>40.25</v>
       </c>
       <c r="C118">
-        <v>-124.08333330000001</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>328794</v>
+        <v>325990</v>
       </c>
       <c r="B119">
-        <v>40.166666669999998</v>
+        <v>40.25</v>
       </c>
       <c r="C119">
-        <v>-124.04166669999999</v>
+        <v>-123.79166669999999</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>328795</v>
+        <v>327382</v>
       </c>
       <c r="B120">
-        <v>40.166666669999998</v>
+        <v>40.2083333333252</v>
       </c>
       <c r="C120">
-        <v>-124</v>
+        <v>-124.33333333333201</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>328796</v>
+        <v>327383</v>
       </c>
       <c r="B121">
-        <v>40.166666669999998</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C121">
-        <v>-123.95833330000001</v>
+        <v>-124.29166669999999</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>328797</v>
+        <v>327384</v>
       </c>
       <c r="B122">
-        <v>40.166666669999998</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C122">
-        <v>-123.91666669999999</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>328798</v>
+        <v>327385</v>
       </c>
       <c r="B123">
-        <v>40.166666669999998</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C123">
-        <v>-123.875</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>328799</v>
+        <v>327386</v>
       </c>
       <c r="B124">
-        <v>40.166666669999998</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C124">
-        <v>-123.83333330000001</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>328800</v>
+        <v>327387</v>
       </c>
       <c r="B125">
-        <v>40.166666669999998</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C125">
-        <v>-123.79166669999999</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>328801</v>
+        <v>327388</v>
       </c>
       <c r="B126">
-        <v>40.166666669999998</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C126">
-        <v>-123.75</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>330196</v>
+        <v>327389</v>
       </c>
       <c r="B127">
-        <v>40.125</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C127">
-        <v>-124.16666669999999</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>330197</v>
+        <v>327390</v>
       </c>
       <c r="B128">
-        <v>40.125</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C128">
-        <v>-124.125</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>330198</v>
+        <v>327391</v>
       </c>
       <c r="B129">
-        <v>40.125</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C129">
-        <v>-124.08333330000001</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>330199</v>
+        <v>327392</v>
       </c>
       <c r="B130">
-        <v>40.125</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C130">
-        <v>-124.04166669999999</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>330200</v>
+        <v>327393</v>
       </c>
       <c r="B131">
-        <v>40.125</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C131">
-        <v>-124</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132">
-        <v>330201</v>
+        <v>327394</v>
       </c>
       <c r="B132">
-        <v>40.125</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C132">
-        <v>-123.95833330000001</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133">
-        <v>330202</v>
+        <v>327395</v>
       </c>
       <c r="B133">
-        <v>40.125</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C133">
-        <v>-123.91666669999999</v>
+        <v>-123.79166669999999</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>330203</v>
+        <v>327396</v>
       </c>
       <c r="B134">
-        <v>40.125</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C134">
-        <v>-123.875</v>
+        <v>-123.75</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>330204</v>
+        <v>328788</v>
       </c>
       <c r="B135">
-        <v>40.125</v>
+        <v>40.1666666666586</v>
       </c>
       <c r="C135">
-        <v>-123.83333330000001</v>
+        <v>-124.291666666666</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136">
-        <v>330205</v>
+        <v>328789</v>
       </c>
       <c r="B136">
-        <v>40.125</v>
+        <v>40.1666666666586</v>
       </c>
       <c r="C136">
-        <v>-123.79166669999999</v>
+        <v>-124.24999999999901</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>330206</v>
+        <v>328790</v>
       </c>
       <c r="B137">
-        <v>40.125</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C137">
-        <v>-123.75</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138">
-        <v>331603</v>
+        <v>328791</v>
       </c>
       <c r="B138">
-        <v>40.083333330000002</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C138">
-        <v>-124.08333330000001</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139">
-        <v>331604</v>
+        <v>328792</v>
       </c>
       <c r="B139">
-        <v>40.083333330000002</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C139">
-        <v>-124.04166669999999</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140">
-        <v>331605</v>
+        <v>328793</v>
       </c>
       <c r="B140">
-        <v>40.083333330000002</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C140">
-        <v>-124</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141">
-        <v>331606</v>
+        <v>328794</v>
       </c>
       <c r="B141">
-        <v>40.083333330000002</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C141">
-        <v>-123.95833330000001</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142">
-        <v>331607</v>
+        <v>328795</v>
       </c>
       <c r="B142">
-        <v>40.083333330000002</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C142">
-        <v>-123.91666669999999</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143">
-        <v>331608</v>
+        <v>328796</v>
       </c>
       <c r="B143">
-        <v>40.083333330000002</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C143">
-        <v>-123.875</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144">
-        <v>331609</v>
+        <v>328797</v>
       </c>
       <c r="B144">
-        <v>40.083333330000002</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C144">
-        <v>-123.83333330000001</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145">
-        <v>331610</v>
+        <v>328798</v>
       </c>
       <c r="B145">
-        <v>40.083333330000002</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C145">
-        <v>-123.79166669999999</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146">
-        <v>331611</v>
+        <v>328799</v>
       </c>
       <c r="B146">
-        <v>40.083333330000002</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C146">
-        <v>-123.75</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147">
-        <v>333009</v>
+        <v>328800</v>
       </c>
       <c r="B147">
-        <v>40.041666669999998</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C147">
-        <v>-124.04166669999999</v>
+        <v>-123.79166669999999</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148">
-        <v>333010</v>
+        <v>328801</v>
       </c>
       <c r="B148">
-        <v>40.041666669999998</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C148">
-        <v>-124</v>
+        <v>-123.75</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149">
-        <v>333011</v>
+        <v>330195</v>
       </c>
       <c r="B149">
-        <v>40.041666669999998</v>
+        <v>40.1249999999918</v>
       </c>
       <c r="C149">
-        <v>-123.95833330000001</v>
+        <v>-124.20833333333201</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150">
-        <v>333012</v>
+        <v>330196</v>
       </c>
       <c r="B150">
-        <v>40.041666669999998</v>
+        <v>40.125</v>
       </c>
       <c r="C150">
-        <v>-123.91666669999999</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151">
-        <v>333013</v>
+        <v>330197</v>
       </c>
       <c r="B151">
-        <v>40.041666669999998</v>
+        <v>40.125</v>
       </c>
       <c r="C151">
-        <v>-123.875</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152">
-        <v>333014</v>
+        <v>330198</v>
       </c>
       <c r="B152">
-        <v>40.041666669999998</v>
+        <v>40.125</v>
       </c>
       <c r="C152">
-        <v>-123.83333330000001</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153">
-        <v>333015</v>
+        <v>330199</v>
       </c>
       <c r="B153">
-        <v>40.041666669999998</v>
+        <v>40.125</v>
       </c>
       <c r="C153">
-        <v>-123.79166669999999</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154">
-        <v>333016</v>
+        <v>330200</v>
       </c>
       <c r="B154">
-        <v>40.041666669999998</v>
+        <v>40.125</v>
       </c>
       <c r="C154">
-        <v>-123.75</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155">
-        <v>334415</v>
+        <v>330201</v>
       </c>
       <c r="B155">
-        <v>40</v>
+        <v>40.125</v>
       </c>
       <c r="C155">
-        <v>-124</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156">
-        <v>334416</v>
+        <v>330202</v>
       </c>
       <c r="B156">
-        <v>40</v>
+        <v>40.125</v>
       </c>
       <c r="C156">
-        <v>-123.95833330000001</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157">
-        <v>334417</v>
+        <v>330203</v>
       </c>
       <c r="B157">
-        <v>40</v>
+        <v>40.125</v>
       </c>
       <c r="C157">
-        <v>-123.91666669999999</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158">
-        <v>334418</v>
+        <v>330204</v>
       </c>
       <c r="B158">
-        <v>40</v>
+        <v>40.125</v>
       </c>
       <c r="C158">
-        <v>-123.875</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159">
-        <v>334419</v>
+        <v>330205</v>
       </c>
       <c r="B159">
-        <v>40</v>
+        <v>40.125</v>
       </c>
       <c r="C159">
-        <v>-123.83333330000001</v>
+        <v>-123.79166669999999</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160">
-        <v>334420</v>
+        <v>330206</v>
       </c>
       <c r="B160">
-        <v>40</v>
+        <v>40.125</v>
       </c>
       <c r="C160">
-        <v>-123.79166669999999</v>
+        <v>-123.75</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161">
-        <v>334421</v>
+        <v>331601</v>
       </c>
       <c r="B161">
-        <v>40</v>
+        <v>40.0833333333252</v>
       </c>
       <c r="C161">
-        <v>-123.75</v>
+        <v>-124.166666666666</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162">
-        <v>334422</v>
+        <v>331602</v>
       </c>
       <c r="B162">
-        <v>40</v>
+        <v>40.0833333333252</v>
       </c>
       <c r="C162">
-        <v>-123.70833330000001</v>
+        <v>-124.12499999999901</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163">
-        <v>335821</v>
+        <v>331603</v>
       </c>
       <c r="B163">
-        <v>39.958333330000002</v>
+        <v>40.083333330000002</v>
       </c>
       <c r="C163">
-        <v>-123.95833330000001</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164">
-        <v>335822</v>
+        <v>331604</v>
       </c>
       <c r="B164">
-        <v>39.958333330000002</v>
+        <v>40.083333330000002</v>
       </c>
       <c r="C164">
-        <v>-123.91666669999999</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165">
-        <v>335823</v>
+        <v>331605</v>
       </c>
       <c r="B165">
-        <v>39.958333330000002</v>
+        <v>40.083333330000002</v>
       </c>
       <c r="C165">
-        <v>-123.875</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166">
-        <v>335824</v>
+        <v>331606</v>
       </c>
       <c r="B166">
-        <v>39.958333330000002</v>
+        <v>40.083333330000002</v>
       </c>
       <c r="C166">
-        <v>-123.83333330000001</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167">
-        <v>335825</v>
+        <v>331607</v>
       </c>
       <c r="B167">
-        <v>39.958333330000002</v>
+        <v>40.083333330000002</v>
       </c>
       <c r="C167">
-        <v>-123.79166669999999</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168">
-        <v>335826</v>
+        <v>331608</v>
       </c>
       <c r="B168">
-        <v>39.958333330000002</v>
+        <v>40.083333330000002</v>
       </c>
       <c r="C168">
-        <v>-123.75</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169">
-        <v>337226</v>
+        <v>331609</v>
       </c>
       <c r="B169">
-        <v>39.916666669999998</v>
+        <v>40.083333330000002</v>
       </c>
       <c r="C169">
-        <v>-123.95833330000001</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170">
-        <v>337227</v>
+        <v>331610</v>
       </c>
       <c r="B170">
-        <v>39.916666669999998</v>
+        <v>40.083333330000002</v>
       </c>
       <c r="C170">
-        <v>-123.91666669999999</v>
+        <v>-123.79166669999999</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171">
-        <v>337228</v>
+        <v>331611</v>
       </c>
       <c r="B171">
-        <v>39.916666669999998</v>
+        <v>40.083333330000002</v>
       </c>
       <c r="C171">
-        <v>-123.875</v>
+        <v>-123.75</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172">
-        <v>337229</v>
+        <v>333008</v>
       </c>
       <c r="B172">
-        <v>39.916666669999998</v>
+        <v>40.0416666666585</v>
       </c>
       <c r="C172">
-        <v>-123.83333330000001</v>
+        <v>-124.08333333333201</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173">
-        <v>337230</v>
+        <v>333009</v>
       </c>
       <c r="B173">
-        <v>39.916666669999998</v>
+        <v>40.041666669999998</v>
       </c>
       <c r="C173">
-        <v>-123.79166669999999</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174">
-        <v>337231</v>
+        <v>333010</v>
       </c>
       <c r="B174">
-        <v>39.916666669999998</v>
+        <v>40.041666669999998</v>
       </c>
       <c r="C174">
-        <v>-123.75</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175">
-        <v>338632</v>
+        <v>333011</v>
       </c>
       <c r="B175">
-        <v>39.875</v>
+        <v>40.041666669999998</v>
       </c>
       <c r="C175">
-        <v>-123.91666669999999</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176">
-        <v>338633</v>
+        <v>333012</v>
       </c>
       <c r="B176">
-        <v>39.875</v>
+        <v>40.041666669999998</v>
       </c>
       <c r="C176">
-        <v>-123.875</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177">
-        <v>338634</v>
+        <v>333013</v>
       </c>
       <c r="B177">
-        <v>39.875</v>
+        <v>40.041666669999998</v>
       </c>
       <c r="C177">
-        <v>-123.83333330000001</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178">
-        <v>338635</v>
+        <v>333014</v>
       </c>
       <c r="B178">
-        <v>39.875</v>
+        <v>40.041666669999998</v>
       </c>
       <c r="C178">
-        <v>-123.79166669999999</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179">
-        <v>340038</v>
+        <v>333015</v>
       </c>
       <c r="B179">
-        <v>39.833333330000002</v>
+        <v>40.041666669999998</v>
       </c>
       <c r="C179">
-        <v>-123.875</v>
+        <v>-123.79166669999999</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180">
-        <v>335820</v>
+        <v>333016</v>
       </c>
       <c r="B180">
-        <v>39.958333333325101</v>
+        <v>40.041666669999998</v>
       </c>
       <c r="C180">
-        <v>-123.99999999999901</v>
+        <v>-123.75</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
@@ -4548,302 +4579,312 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182">
-        <v>333008</v>
+        <v>334415</v>
       </c>
       <c r="B182">
-        <v>40.0416666666585</v>
+        <v>40</v>
       </c>
       <c r="C182">
-        <v>-124.08333333333201</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183">
-        <v>331601</v>
+        <v>334416</v>
       </c>
       <c r="B183">
-        <v>40.0833333333252</v>
+        <v>40</v>
       </c>
       <c r="C183">
-        <v>-124.166666666666</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184">
-        <v>331602</v>
+        <v>334417</v>
       </c>
       <c r="B184">
-        <v>40.0833333333252</v>
+        <v>40</v>
       </c>
       <c r="C184">
-        <v>-124.12499999999901</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185">
-        <v>330195</v>
+        <v>334418</v>
       </c>
       <c r="B185">
-        <v>40.1249999999918</v>
+        <v>40</v>
       </c>
       <c r="C185">
-        <v>-124.20833333333201</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186">
-        <v>328789</v>
+        <v>334419</v>
       </c>
       <c r="B186">
-        <v>40.1666666666586</v>
+        <v>40</v>
       </c>
       <c r="C186">
-        <v>-124.24999999999901</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187">
-        <v>328788</v>
+        <v>334420</v>
       </c>
       <c r="B187">
-        <v>40.1666666666586</v>
+        <v>40</v>
       </c>
       <c r="C187">
-        <v>-124.291666666666</v>
+        <v>-123.79166669999999</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188">
-        <v>327382</v>
+        <v>334421</v>
       </c>
       <c r="B188">
-        <v>40.2083333333252</v>
+        <v>40</v>
       </c>
       <c r="C188">
-        <v>-124.33333333333201</v>
+        <v>-123.75</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189">
-        <v>325976</v>
+        <v>334422</v>
       </c>
       <c r="B189">
-        <v>40.2499999999919</v>
+        <v>40</v>
       </c>
       <c r="C189">
-        <v>-124.37499999999901</v>
+        <v>-123.70833330000001</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190">
-        <v>324571</v>
+        <v>335820</v>
       </c>
       <c r="B190">
-        <v>40.2916666666586</v>
+        <v>39.958333333325101</v>
       </c>
       <c r="C190">
-        <v>-124.37499999999901</v>
+        <v>-123.99999999999901</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191">
-        <v>323166</v>
+        <v>335821</v>
       </c>
       <c r="B191">
-        <v>40.333333333325299</v>
+        <v>39.958333330000002</v>
       </c>
       <c r="C191">
-        <v>-124.37499999999901</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192">
-        <v>321761</v>
+        <v>335822</v>
       </c>
       <c r="B192">
-        <v>40.374999999991999</v>
+        <v>39.958333330000002</v>
       </c>
       <c r="C192">
-        <v>-124.37499999999901</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193">
-        <v>320355</v>
+        <v>335823</v>
       </c>
       <c r="B193">
-        <v>40.416666666658699</v>
+        <v>39.958333330000002</v>
       </c>
       <c r="C193">
-        <v>-124.416666666666</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194">
-        <v>318950</v>
+        <v>335824</v>
       </c>
       <c r="B194">
-        <v>40.458333333325399</v>
+        <v>39.958333330000002</v>
       </c>
       <c r="C194">
-        <v>-124.416666666666</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195">
-        <v>317545</v>
+        <v>335825</v>
       </c>
       <c r="B195">
-        <v>40.499999999992099</v>
+        <v>39.958333330000002</v>
       </c>
       <c r="C195">
-        <v>-124.416666666666</v>
+        <v>-123.79166669999999</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196">
-        <v>317546</v>
+        <v>335826</v>
       </c>
       <c r="B196">
-        <v>40.499999999992099</v>
+        <v>39.958333330000002</v>
       </c>
       <c r="C196">
-        <v>-124.37499999999901</v>
+        <v>-123.75</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197">
-        <v>316141</v>
+        <v>337226</v>
       </c>
       <c r="B197">
-        <v>40.541666666658799</v>
+        <v>39.916666669999998</v>
       </c>
       <c r="C197">
-        <v>-124.37499999999901</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198">
-        <v>316142</v>
+        <v>337227</v>
       </c>
       <c r="B198">
-        <v>40.541666666658799</v>
+        <v>39.916666669999998</v>
       </c>
       <c r="C198">
-        <v>-124.33333333333201</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199">
-        <v>316143</v>
+        <v>337228</v>
       </c>
       <c r="B199">
-        <v>40.541666666658799</v>
+        <v>39.916666669999998</v>
       </c>
       <c r="C199">
-        <v>-124.291666666666</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200">
-        <v>314736</v>
+        <v>337229</v>
       </c>
       <c r="B200">
-        <v>40.583333333325498</v>
+        <v>39.916666669999998</v>
       </c>
       <c r="C200">
-        <v>-124.37499999999901</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201">
-        <v>314738</v>
+        <v>337230</v>
       </c>
       <c r="B201">
-        <v>40.583333333325498</v>
+        <v>39.916666669999998</v>
       </c>
       <c r="C201">
-        <v>-124.291666666666</v>
+        <v>-123.79166669999999</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202">
-        <v>314737</v>
+        <v>337231</v>
       </c>
       <c r="B202">
-        <v>40.583333333325498</v>
+        <v>39.916666669999998</v>
       </c>
       <c r="C202">
-        <v>-124.33333333333201</v>
+        <v>-123.75</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203">
-        <v>314739</v>
+        <v>338632</v>
       </c>
       <c r="B203">
-        <v>40.583333333325498</v>
+        <v>39.875</v>
       </c>
       <c r="C203">
-        <v>-124.24999999999901</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204">
-        <v>313332</v>
+        <v>338633</v>
       </c>
       <c r="B204">
-        <v>40.624999999992198</v>
+        <v>39.875</v>
       </c>
       <c r="C204">
-        <v>-124.33333333333201</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205">
-        <v>313333</v>
+        <v>338634</v>
       </c>
       <c r="B205">
-        <v>40.624999999992198</v>
+        <v>39.875</v>
       </c>
       <c r="C205">
-        <v>-124.291666666666</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206">
-        <v>311927</v>
+        <v>338635</v>
       </c>
       <c r="B206">
-        <v>40.666666666658898</v>
+        <v>39.875</v>
       </c>
       <c r="C206">
-        <v>-124.33333333333201</v>
+        <v>-123.79166669999999</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207">
-        <v>311928</v>
+        <v>340038</v>
       </c>
       <c r="B207">
-        <v>40.666666666658898</v>
+        <v>39.833333330000002</v>
       </c>
       <c r="C207">
-        <v>-124.291666666666</v>
+        <v>-123.875</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C207" xr:uid="{C6D3A6DD-588C-4514-87BD-3A8DDF36FFF6}"/>
+  <autoFilter ref="A1:C207" xr:uid="{C6D3A6DD-588C-4514-87BD-3A8DDF36FFF6}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C207">
+      <sortCondition ref="A1:A207"/>
+    </sortState>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K2:M208">
+    <sortCondition ref="K1:K208"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4693A724-9298-4483-9B9E-D6EAC7997E3D}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -4854,7 +4895,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>48264</v>
       </c>
@@ -4864,8 +4905,9 @@
       <c r="C2">
         <v>-123.938</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>47799</v>
       </c>
@@ -4875,8 +4917,9 @@
       <c r="C3">
         <v>-124.063</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>47800</v>
       </c>
@@ -4886,8 +4929,9 @@
       <c r="C4">
         <v>-123.938</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>47334</v>
       </c>
@@ -4897,8 +4941,9 @@
       <c r="C5">
         <v>-124.188</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>47335</v>
       </c>
@@ -4908,8 +4953,9 @@
       <c r="C6">
         <v>-124.063</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>47333</v>
       </c>
@@ -4919,8 +4965,9 @@
       <c r="C7">
         <v>-124.313</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>47336</v>
       </c>
@@ -4930,8 +4977,9 @@
       <c r="C8">
         <v>-123.938</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>47337</v>
       </c>
@@ -4941,8 +4989,9 @@
       <c r="C9">
         <v>-123.813</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>46869</v>
       </c>
@@ -4952,8 +5001,9 @@
       <c r="C10">
         <v>-124.313</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>46870</v>
       </c>
@@ -4963,8 +5013,9 @@
       <c r="C11">
         <v>-124.188</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>46871</v>
       </c>
@@ -4974,8 +5025,9 @@
       <c r="C12">
         <v>-124.063</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>46872</v>
       </c>
@@ -4985,8 +5037,9 @@
       <c r="C13">
         <v>-123.938</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>46405</v>
       </c>
@@ -4996,8 +5049,9 @@
       <c r="C14">
         <v>-124.313</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>46406</v>
       </c>
@@ -5007,8 +5061,9 @@
       <c r="C15">
         <v>-124.188</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>46407</v>
       </c>
@@ -5018,8 +5073,9 @@
       <c r="C16">
         <v>-124.063</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>46408</v>
       </c>
@@ -5029,8 +5085,9 @@
       <c r="C17">
         <v>-123.938</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>46404</v>
       </c>
@@ -5040,8 +5097,9 @@
       <c r="C18">
         <v>-124.438</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>45940</v>
       </c>
@@ -5051,8 +5109,9 @@
       <c r="C19">
         <v>-124.438</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>45941</v>
       </c>
@@ -5062,8 +5121,9 @@
       <c r="C20">
         <v>-124.313</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>45942</v>
       </c>
@@ -5073,8 +5133,9 @@
       <c r="C21">
         <v>-124.188</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>45477</v>
       </c>
@@ -5084,8 +5145,9 @@
       <c r="C22">
         <v>-124.313</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>45476</v>
       </c>
@@ -5095,8 +5157,9 @@
       <c r="C23">
         <v>-124.438</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>45478</v>
       </c>
@@ -5106,8 +5169,9 @@
       <c r="C24">
         <v>-124.188</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>45943</v>
       </c>
@@ -5117,8 +5181,9 @@
       <c r="C25">
         <v>-124.063</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>46403</v>
       </c>
@@ -5128,8 +5193,9 @@
       <c r="C26">
         <v>-124.563</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>46868</v>
       </c>
@@ -5139,8 +5205,9 @@
       <c r="C27">
         <v>-124.438</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>46873</v>
       </c>
@@ -5150,8 +5217,9 @@
       <c r="C28">
         <v>-123.813</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>47332</v>
       </c>
@@ -5161,8 +5229,9 @@
       <c r="C29">
         <v>-124.438</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>47797</v>
       </c>
@@ -5172,8 +5241,9 @@
       <c r="C30">
         <v>-124.313</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>47798</v>
       </c>
@@ -5183,8 +5253,9 @@
       <c r="C31">
         <v>-124.188</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>47801</v>
       </c>
@@ -5194,8 +5265,9 @@
       <c r="C32">
         <v>-123.813</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>48262</v>
       </c>
@@ -5205,8 +5277,9 @@
       <c r="C33">
         <v>-124.188</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>48263</v>
       </c>
@@ -5216,8 +5289,9 @@
       <c r="C34">
         <v>-124.063</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>48265</v>
       </c>
@@ -5227,6 +5301,7 @@
       <c r="C35">
         <v>-123.813</v>
       </c>
+      <c r="F35" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7196,6 +7271,10 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.88671875" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" customWidth="1"/>
+    <col min="16" max="16" width="25.109375" customWidth="1"/>
+    <col min="17" max="17" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -9307,14 +9386,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"Blank Document","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD1B9453B0FD26428396C40DDB69C7F0" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="802f121d94e69ef52d0e517f320156b7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="04ff8bd0-14ef-4472-a603-3a4b6f9fed19" xmlns:ns3="84c16208-172a-4eaa-b33e-1408ce0b909e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="52afc94f32e932e2c2aa5cc0dde246b5" ns2:_="" ns3:_="">
     <xsd:import namespace="04ff8bd0-14ef-4472-a603-3a4b6f9fed19"/>
@@ -9547,16 +9618,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"Blank Document","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
 </file>
 
-<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="84c16208-172a-4eaa-b33e-1408ce0b909e" xsi:nil="true"/>
@@ -9575,19 +9645,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06124858-FF52-43B6-9F5F-14F707108C35}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
+<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43BD7F1F-596C-48D7-B49B-C059BD9AD9F3}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E96BF69-B1EB-4515-B4A0-E6542DFE7270}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9606,15 +9673,19 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41E32FE7-C838-46D6-8359-8A7BBC9B619E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43BD7F1F-596C-48D7-B49B-C059BD9AD9F3}">
+  <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06124858-FF52-43B6-9F5F-14F707108C35}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A7D180A-E261-4A2D-8CBC-AEEBF9B497B3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -9631,6 +9702,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41E32FE7-C838-46D6-8359-8A7BBC9B619E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0bb6ca0c-ccb3-428b-9d5f-a9c60cad6645}" enabled="1" method="Standard" siteId="{fe186a25-7d49-41e6-9941-05d2281d36c1}" contentBits="0" removed="0"/>

--- a/W3_LSPC_Watershed/inputs/Project_Control_Mattole.xlsx
+++ b/W3_LSPC_Watershed/inputs/Project_Control_Mattole.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33CF025-8814-4D88-95DD-118C6F334615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE00D7B-944D-47C0-84D7-D1EF87D4A61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="GageMapping" sheetId="11" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Prism!$A$1:$C$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Prism!$A$1:$C$207</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="85">
   <si>
     <t>cimis_id</t>
   </si>
@@ -287,6 +287,12 @@
     <t>raw/gage/other</t>
   </si>
   <si>
+    <t>GHCND:US1CAHM0127</t>
+  </si>
+  <si>
+    <t>LOLETA 1.3 ESE, CA US</t>
+  </si>
+  <si>
     <t>../data/shared</t>
   </si>
   <si>
@@ -297,7 +303,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -305,16 +311,316 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -322,17 +628,206 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -742,7 +1237,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -810,7 +1305,7 @@
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -2580,7 +3075,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A6DD-588C-4514-87BD-3A8DDF36FFF6}">
-  <dimension ref="A1:C207"/>
+  <dimension ref="A1:C222"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -2599,1143 +3094,1143 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>311927</v>
+        <v>309119</v>
       </c>
       <c r="B2">
-        <v>40.666666666658898</v>
+        <v>40.75</v>
       </c>
       <c r="C2">
-        <v>-124.33333333333201</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>311928</v>
+        <v>309120</v>
       </c>
       <c r="B3">
-        <v>40.666666666658898</v>
+        <v>40.75</v>
       </c>
       <c r="C3">
-        <v>-124.291666666666</v>
+        <v>-124.208</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>313332</v>
+        <v>310523</v>
       </c>
       <c r="B4">
-        <v>40.624999999992198</v>
+        <v>40.708329999999997</v>
       </c>
       <c r="C4">
-        <v>-124.33333333333201</v>
+        <v>-124.292</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>313333</v>
+        <v>310524</v>
       </c>
       <c r="B5">
-        <v>40.624999999992198</v>
+        <v>40.708329999999997</v>
       </c>
       <c r="C5">
-        <v>-124.291666666666</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>314736</v>
+        <v>310525</v>
       </c>
       <c r="B6">
-        <v>40.583333333325498</v>
+        <v>40.708329999999997</v>
       </c>
       <c r="C6">
-        <v>-124.37499999999901</v>
+        <v>-124.208</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>314737</v>
+        <v>310526</v>
       </c>
       <c r="B7">
-        <v>40.583333333325498</v>
+        <v>40.708329999999997</v>
       </c>
       <c r="C7">
-        <v>-124.33333333333201</v>
+        <v>-124.167</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>314738</v>
+        <v>311927</v>
       </c>
       <c r="B8">
-        <v>40.583333333325498</v>
+        <v>40.666666666658898</v>
       </c>
       <c r="C8">
-        <v>-124.291666666666</v>
+        <v>-124.33333333333201</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>314739</v>
+        <v>311928</v>
       </c>
       <c r="B9">
-        <v>40.583333333325498</v>
+        <v>40.666666666658898</v>
       </c>
       <c r="C9">
-        <v>-124.24999999999901</v>
+        <v>-124.291666666666</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>314741</v>
+        <v>311929</v>
       </c>
       <c r="B10">
-        <v>40.583333330000002</v>
+        <v>40.666666669999998</v>
       </c>
       <c r="C10">
-        <v>-124.16666669999999</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>314742</v>
+        <v>311930</v>
       </c>
       <c r="B11">
-        <v>40.583333330000002</v>
+        <v>40.666666669999998</v>
       </c>
       <c r="C11">
-        <v>-124.125</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>316141</v>
+        <v>311931</v>
       </c>
       <c r="B12">
-        <v>40.541666666658799</v>
+        <v>40.666666669999998</v>
       </c>
       <c r="C12">
-        <v>-124.37499999999901</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>316142</v>
+        <v>311932</v>
       </c>
       <c r="B13">
-        <v>40.541666666658799</v>
+        <v>40.666666669999998</v>
       </c>
       <c r="C13">
-        <v>-124.33333333333201</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>316143</v>
+        <v>313332</v>
       </c>
       <c r="B14">
-        <v>40.541666666658799</v>
+        <v>40.624999999992198</v>
       </c>
       <c r="C14">
-        <v>-124.291666666666</v>
+        <v>-124.33333333333201</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>316144</v>
+        <v>313333</v>
       </c>
       <c r="B15">
-        <v>40.541666669999998</v>
+        <v>40.624999999992198</v>
       </c>
       <c r="C15">
-        <v>-124.25</v>
+        <v>-124.291666666666</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>316145</v>
+        <v>313334</v>
       </c>
       <c r="B16">
-        <v>40.541666669999998</v>
+        <v>40.625</v>
       </c>
       <c r="C16">
-        <v>-124.20833330000001</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>316146</v>
+        <v>313335</v>
       </c>
       <c r="B17">
-        <v>40.541666669999998</v>
+        <v>40.625</v>
       </c>
       <c r="C17">
-        <v>-124.16666669999999</v>
+        <v>-124.208</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>316147</v>
+        <v>313336</v>
       </c>
       <c r="B18">
-        <v>40.541666669999998</v>
+        <v>40.625</v>
       </c>
       <c r="C18">
-        <v>-124.125</v>
+        <v>-124.167</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>316148</v>
+        <v>313337</v>
       </c>
       <c r="B19">
-        <v>40.541666669999998</v>
+        <v>40.625</v>
       </c>
       <c r="C19">
-        <v>-124.08333330000001</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>316149</v>
+        <v>314736</v>
       </c>
       <c r="B20">
-        <v>40.541666669999998</v>
+        <v>40.583333333325498</v>
       </c>
       <c r="C20">
-        <v>-124.04166669999999</v>
+        <v>-124.37499999999901</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>316150</v>
+        <v>314737</v>
       </c>
       <c r="B21">
-        <v>40.541666669999998</v>
+        <v>40.583333333325498</v>
       </c>
       <c r="C21">
-        <v>-124</v>
+        <v>-124.33333333333201</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>317545</v>
+        <v>314738</v>
       </c>
       <c r="B22">
-        <v>40.499999999992099</v>
+        <v>40.583333333325498</v>
       </c>
       <c r="C22">
-        <v>-124.416666666666</v>
+        <v>-124.291666666666</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>317546</v>
+        <v>314739</v>
       </c>
       <c r="B23">
-        <v>40.499999999992099</v>
+        <v>40.583333333325498</v>
       </c>
       <c r="C23">
-        <v>-124.37499999999901</v>
+        <v>-124.24999999999901</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>317547</v>
+        <v>314740</v>
       </c>
       <c r="B24">
-        <v>40.5</v>
+        <v>40.583329999999997</v>
       </c>
       <c r="C24">
-        <v>-124.33333330000001</v>
+        <v>-124.208</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>317548</v>
+        <v>314741</v>
       </c>
       <c r="B25">
-        <v>40.5</v>
+        <v>40.583333330000002</v>
       </c>
       <c r="C25">
-        <v>-124.29166669999999</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>317549</v>
+        <v>314742</v>
       </c>
       <c r="B26">
-        <v>40.5</v>
+        <v>40.583333330000002</v>
       </c>
       <c r="C26">
-        <v>-124.25</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>317550</v>
+        <v>316141</v>
       </c>
       <c r="B27">
-        <v>40.5</v>
+        <v>40.541666666658799</v>
       </c>
       <c r="C27">
-        <v>-124.20833330000001</v>
+        <v>-124.37499999999901</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>317551</v>
+        <v>316142</v>
       </c>
       <c r="B28">
-        <v>40.5</v>
+        <v>40.541666666658799</v>
       </c>
       <c r="C28">
-        <v>-124.16666669999999</v>
+        <v>-124.33333333333201</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>317552</v>
+        <v>316143</v>
       </c>
       <c r="B29">
-        <v>40.5</v>
+        <v>40.541666666658799</v>
       </c>
       <c r="C29">
-        <v>-124.125</v>
+        <v>-124.291666666666</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>317553</v>
+        <v>316144</v>
       </c>
       <c r="B30">
-        <v>40.5</v>
+        <v>40.541666669999998</v>
       </c>
       <c r="C30">
-        <v>-124.08333330000001</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>317554</v>
+        <v>316145</v>
       </c>
       <c r="B31">
-        <v>40.5</v>
+        <v>40.541666669999998</v>
       </c>
       <c r="C31">
-        <v>-124.04166669999999</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>317555</v>
+        <v>316146</v>
       </c>
       <c r="B32">
-        <v>40.5</v>
+        <v>40.541666669999998</v>
       </c>
       <c r="C32">
-        <v>-124</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>317556</v>
+        <v>316147</v>
       </c>
       <c r="B33">
-        <v>40.5</v>
+        <v>40.541666669999998</v>
       </c>
       <c r="C33">
-        <v>-123.95833330000001</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>317557</v>
+        <v>316148</v>
       </c>
       <c r="B34">
-        <v>40.5</v>
+        <v>40.541666669999998</v>
       </c>
       <c r="C34">
-        <v>-123.91666669999999</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>318950</v>
+        <v>316149</v>
       </c>
       <c r="B35">
-        <v>40.458333333325399</v>
+        <v>40.541666669999998</v>
       </c>
       <c r="C35">
-        <v>-124.416666666666</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>318951</v>
+        <v>316150</v>
       </c>
       <c r="B36">
-        <v>40.458333330000002</v>
+        <v>40.541666669999998</v>
       </c>
       <c r="C36">
-        <v>-124.375</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>318952</v>
+        <v>317545</v>
       </c>
       <c r="B37">
-        <v>40.458333330000002</v>
+        <v>40.499999999992099</v>
       </c>
       <c r="C37">
-        <v>-124.33333330000001</v>
+        <v>-124.416666666666</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>318953</v>
+        <v>317546</v>
       </c>
       <c r="B38">
-        <v>40.458333330000002</v>
+        <v>40.499999999992099</v>
       </c>
       <c r="C38">
-        <v>-124.29166669999999</v>
+        <v>-124.37499999999901</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>318954</v>
+        <v>317547</v>
       </c>
       <c r="B39">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C39">
-        <v>-124.25</v>
+        <v>-124.33333330000001</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>318955</v>
+        <v>317548</v>
       </c>
       <c r="B40">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C40">
-        <v>-124.20833330000001</v>
+        <v>-124.29166669999999</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>318956</v>
+        <v>317549</v>
       </c>
       <c r="B41">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C41">
-        <v>-124.16666669999999</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>318957</v>
+        <v>317550</v>
       </c>
       <c r="B42">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C42">
-        <v>-124.125</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>318958</v>
+        <v>317551</v>
       </c>
       <c r="B43">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C43">
-        <v>-124.08333330000001</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>318959</v>
+        <v>317552</v>
       </c>
       <c r="B44">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C44">
-        <v>-124.04166669999999</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>318960</v>
+        <v>317553</v>
       </c>
       <c r="B45">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C45">
-        <v>-124</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>318961</v>
+        <v>317554</v>
       </c>
       <c r="B46">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C46">
-        <v>-123.95833330000001</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>318962</v>
+        <v>317555</v>
       </c>
       <c r="B47">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C47">
-        <v>-123.91666669999999</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>318963</v>
+        <v>317556</v>
       </c>
       <c r="B48">
-        <v>40.458333330000002</v>
+        <v>40.5</v>
       </c>
       <c r="C48">
-        <v>-123.875</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>320355</v>
+        <v>317557</v>
       </c>
       <c r="B49">
-        <v>40.416666666658699</v>
+        <v>40.5</v>
       </c>
       <c r="C49">
-        <v>-124.416666666666</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>320356</v>
+        <v>318950</v>
       </c>
       <c r="B50">
-        <v>40.416666669999998</v>
+        <v>40.458333333325399</v>
       </c>
       <c r="C50">
-        <v>-124.375</v>
+        <v>-124.416666666666</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>320357</v>
+        <v>318951</v>
       </c>
       <c r="B51">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C51">
-        <v>-124.33333330000001</v>
+        <v>-124.375</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>320358</v>
+        <v>318952</v>
       </c>
       <c r="B52">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C52">
-        <v>-124.29166669999999</v>
+        <v>-124.33333330000001</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>320359</v>
+        <v>318953</v>
       </c>
       <c r="B53">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C53">
-        <v>-124.25</v>
+        <v>-124.29166669999999</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>320360</v>
+        <v>318954</v>
       </c>
       <c r="B54">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C54">
-        <v>-124.20833330000001</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>320361</v>
+        <v>318955</v>
       </c>
       <c r="B55">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C55">
-        <v>-124.16666669999999</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>320362</v>
+        <v>318956</v>
       </c>
       <c r="B56">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C56">
-        <v>-124.125</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>320363</v>
+        <v>318957</v>
       </c>
       <c r="B57">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C57">
-        <v>-124.08333330000001</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>320364</v>
+        <v>318958</v>
       </c>
       <c r="B58">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C58">
-        <v>-124.04166669999999</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>320365</v>
+        <v>318959</v>
       </c>
       <c r="B59">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C59">
-        <v>-124</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>320366</v>
+        <v>318960</v>
       </c>
       <c r="B60">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C60">
-        <v>-123.95833330000001</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>320367</v>
+        <v>318961</v>
       </c>
       <c r="B61">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C61">
-        <v>-123.91666669999999</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>320368</v>
+        <v>318962</v>
       </c>
       <c r="B62">
-        <v>40.416666669999998</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C62">
-        <v>-123.875</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>321761</v>
+        <v>318963</v>
       </c>
       <c r="B63">
-        <v>40.374999999991999</v>
+        <v>40.458333330000002</v>
       </c>
       <c r="C63">
-        <v>-124.37499999999901</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>321762</v>
+        <v>320355</v>
       </c>
       <c r="B64">
-        <v>40.375</v>
+        <v>40.416666666658699</v>
       </c>
       <c r="C64">
-        <v>-124.33333330000001</v>
+        <v>-124.416666666666</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>321763</v>
+        <v>320356</v>
       </c>
       <c r="B65">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C65">
-        <v>-124.29166669999999</v>
+        <v>-124.375</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>321764</v>
+        <v>320357</v>
       </c>
       <c r="B66">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C66">
-        <v>-124.25</v>
+        <v>-124.33333330000001</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>321765</v>
+        <v>320358</v>
       </c>
       <c r="B67">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C67">
-        <v>-124.20833330000001</v>
+        <v>-124.29166669999999</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>321766</v>
+        <v>320359</v>
       </c>
       <c r="B68">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C68">
-        <v>-124.16666669999999</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>321767</v>
+        <v>320360</v>
       </c>
       <c r="B69">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C69">
-        <v>-124.125</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>321768</v>
+        <v>320361</v>
       </c>
       <c r="B70">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C70">
-        <v>-124.08333330000001</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>321769</v>
+        <v>320362</v>
       </c>
       <c r="B71">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C71">
-        <v>-124.04166669999999</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>321770</v>
+        <v>320363</v>
       </c>
       <c r="B72">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C72">
-        <v>-124</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>321771</v>
+        <v>320364</v>
       </c>
       <c r="B73">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C73">
-        <v>-123.95833330000001</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>321772</v>
+        <v>320365</v>
       </c>
       <c r="B74">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C74">
-        <v>-123.91666669999999</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>321773</v>
+        <v>320366</v>
       </c>
       <c r="B75">
-        <v>40.375</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C75">
-        <v>-123.875</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>323166</v>
+        <v>320367</v>
       </c>
       <c r="B76">
-        <v>40.333333333325299</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C76">
-        <v>-124.37499999999901</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>323167</v>
+        <v>320368</v>
       </c>
       <c r="B77">
-        <v>40.333333330000002</v>
+        <v>40.416666669999998</v>
       </c>
       <c r="C77">
-        <v>-124.33333330000001</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>323168</v>
+        <v>321761</v>
       </c>
       <c r="B78">
-        <v>40.333333330000002</v>
+        <v>40.374999999991999</v>
       </c>
       <c r="C78">
-        <v>-124.29166669999999</v>
+        <v>-124.37499999999901</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>323169</v>
+        <v>321762</v>
       </c>
       <c r="B79">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C79">
-        <v>-124.25</v>
+        <v>-124.33333330000001</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>323170</v>
+        <v>321763</v>
       </c>
       <c r="B80">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C80">
-        <v>-124.20833330000001</v>
+        <v>-124.29166669999999</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>323171</v>
+        <v>321764</v>
       </c>
       <c r="B81">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C81">
-        <v>-124.16666669999999</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>323172</v>
+        <v>321765</v>
       </c>
       <c r="B82">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C82">
-        <v>-124.125</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>323173</v>
+        <v>321766</v>
       </c>
       <c r="B83">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C83">
-        <v>-124.08333330000001</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>323174</v>
+        <v>321767</v>
       </c>
       <c r="B84">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C84">
-        <v>-124.04166669999999</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>323175</v>
+        <v>321768</v>
       </c>
       <c r="B85">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C85">
-        <v>-124</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>323176</v>
+        <v>321769</v>
       </c>
       <c r="B86">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C86">
-        <v>-123.95833330000001</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>323177</v>
+        <v>321770</v>
       </c>
       <c r="B87">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C87">
-        <v>-123.91666669999999</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>323178</v>
+        <v>321771</v>
       </c>
       <c r="B88">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C88">
-        <v>-123.875</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>323179</v>
+        <v>321772</v>
       </c>
       <c r="B89">
-        <v>40.333333330000002</v>
+        <v>40.375</v>
       </c>
       <c r="C89">
-        <v>-123.83333330000001</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>324571</v>
+        <v>321773</v>
       </c>
       <c r="B90">
-        <v>40.2916666666586</v>
+        <v>40.375</v>
       </c>
       <c r="C90">
-        <v>-124.37499999999901</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>324572</v>
+        <v>323166</v>
       </c>
       <c r="B91">
-        <v>40.291666669999998</v>
+        <v>40.333333333325299</v>
       </c>
       <c r="C91">
-        <v>-124.33333330000001</v>
+        <v>-124.37499999999901</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>324573</v>
+        <v>323167</v>
       </c>
       <c r="B92">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C92">
-        <v>-124.29166669999999</v>
+        <v>-124.33333330000001</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>324574</v>
+        <v>323168</v>
       </c>
       <c r="B93">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C93">
-        <v>-124.25</v>
+        <v>-124.29166669999999</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>324575</v>
+        <v>323169</v>
       </c>
       <c r="B94">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C94">
-        <v>-124.20833330000001</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>324576</v>
+        <v>323170</v>
       </c>
       <c r="B95">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C95">
-        <v>-124.16666669999999</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>324577</v>
+        <v>323171</v>
       </c>
       <c r="B96">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C96">
-        <v>-124.125</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>324578</v>
+        <v>323172</v>
       </c>
       <c r="B97">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C97">
-        <v>-124.08333330000001</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>324579</v>
+        <v>323173</v>
       </c>
       <c r="B98">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C98">
-        <v>-124.04166669999999</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>324580</v>
+        <v>323174</v>
       </c>
       <c r="B99">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C99">
-        <v>-124</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>324581</v>
+        <v>323175</v>
       </c>
       <c r="B100">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C100">
-        <v>-123.95833330000001</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>324582</v>
+        <v>323176</v>
       </c>
       <c r="B101">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C101">
-        <v>-123.91666669999999</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>324583</v>
+        <v>323177</v>
       </c>
       <c r="B102">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C102">
-        <v>-123.875</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>324584</v>
+        <v>323178</v>
       </c>
       <c r="B103">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C103">
-        <v>-123.83333330000001</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>324585</v>
+        <v>323179</v>
       </c>
       <c r="B104">
-        <v>40.291666669999998</v>
+        <v>40.333333330000002</v>
       </c>
       <c r="C104">
-        <v>-123.79166669999999</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>325976</v>
+        <v>324571</v>
       </c>
       <c r="B105">
-        <v>40.2499999999919</v>
+        <v>40.2916666666586</v>
       </c>
       <c r="C105">
         <v>-124.37499999999901</v>
@@ -3743,10 +4238,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>325977</v>
+        <v>324572</v>
       </c>
       <c r="B106">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C106">
         <v>-124.33333330000001</v>
@@ -3754,10 +4249,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>325978</v>
+        <v>324573</v>
       </c>
       <c r="B107">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C107">
         <v>-124.29166669999999</v>
@@ -3765,10 +4260,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>325979</v>
+        <v>324574</v>
       </c>
       <c r="B108">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C108">
         <v>-124.25</v>
@@ -3776,10 +4271,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>325980</v>
+        <v>324575</v>
       </c>
       <c r="B109">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C109">
         <v>-124.20833330000001</v>
@@ -3787,10 +4282,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>325981</v>
+        <v>324576</v>
       </c>
       <c r="B110">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C110">
         <v>-124.16666669999999</v>
@@ -3798,10 +4293,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>325982</v>
+        <v>324577</v>
       </c>
       <c r="B111">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C111">
         <v>-124.125</v>
@@ -3809,10 +4304,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>325983</v>
+        <v>324578</v>
       </c>
       <c r="B112">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C112">
         <v>-124.08333330000001</v>
@@ -3820,10 +4315,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>325984</v>
+        <v>324579</v>
       </c>
       <c r="B113">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C113">
         <v>-124.04166669999999</v>
@@ -3831,10 +4326,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>325985</v>
+        <v>324580</v>
       </c>
       <c r="B114">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C114">
         <v>-124</v>
@@ -3842,10 +4337,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>325986</v>
+        <v>324581</v>
       </c>
       <c r="B115">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C115">
         <v>-123.95833330000001</v>
@@ -3853,10 +4348,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>325987</v>
+        <v>324582</v>
       </c>
       <c r="B116">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C116">
         <v>-123.91666669999999</v>
@@ -3864,10 +4359,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>325988</v>
+        <v>324583</v>
       </c>
       <c r="B117">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C117">
         <v>-123.875</v>
@@ -3875,10 +4370,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>325989</v>
+        <v>324584</v>
       </c>
       <c r="B118">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C118">
         <v>-123.83333330000001</v>
@@ -3886,10 +4381,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>325990</v>
+        <v>324585</v>
       </c>
       <c r="B119">
-        <v>40.25</v>
+        <v>40.291666669999998</v>
       </c>
       <c r="C119">
         <v>-123.79166669999999</v>
@@ -3897,994 +4392,1153 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>327382</v>
+        <v>325976</v>
       </c>
       <c r="B120">
-        <v>40.2083333333252</v>
+        <v>40.2499999999919</v>
       </c>
       <c r="C120">
-        <v>-124.33333333333201</v>
+        <v>-124.37499999999901</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>327383</v>
+        <v>325977</v>
       </c>
       <c r="B121">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C121">
-        <v>-124.29166669999999</v>
+        <v>-124.33333330000001</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>327384</v>
+        <v>325978</v>
       </c>
       <c r="B122">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C122">
-        <v>-124.25</v>
+        <v>-124.29166669999999</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>327385</v>
+        <v>325979</v>
       </c>
       <c r="B123">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C123">
-        <v>-124.20833330000001</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>327386</v>
+        <v>325980</v>
       </c>
       <c r="B124">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C124">
-        <v>-124.16666669999999</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>327387</v>
+        <v>325981</v>
       </c>
       <c r="B125">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C125">
-        <v>-124.125</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>327388</v>
+        <v>325982</v>
       </c>
       <c r="B126">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C126">
-        <v>-124.08333330000001</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>327389</v>
+        <v>325983</v>
       </c>
       <c r="B127">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C127">
-        <v>-124.04166669999999</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>327390</v>
+        <v>325984</v>
       </c>
       <c r="B128">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C128">
-        <v>-124</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>327391</v>
+        <v>325985</v>
       </c>
       <c r="B129">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C129">
-        <v>-123.95833330000001</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>327392</v>
+        <v>325986</v>
       </c>
       <c r="B130">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C130">
-        <v>-123.91666669999999</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>327393</v>
+        <v>325987</v>
       </c>
       <c r="B131">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C131">
-        <v>-123.875</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132">
-        <v>327394</v>
+        <v>325988</v>
       </c>
       <c r="B132">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C132">
-        <v>-123.83333330000001</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133">
-        <v>327395</v>
+        <v>325989</v>
       </c>
       <c r="B133">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C133">
-        <v>-123.79166669999999</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>327396</v>
+        <v>325990</v>
       </c>
       <c r="B134">
-        <v>40.208333330000002</v>
+        <v>40.25</v>
       </c>
       <c r="C134">
-        <v>-123.75</v>
+        <v>-123.79166669999999</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>328788</v>
+        <v>327382</v>
       </c>
       <c r="B135">
-        <v>40.1666666666586</v>
+        <v>40.2083333333252</v>
       </c>
       <c r="C135">
-        <v>-124.291666666666</v>
+        <v>-124.33333333333201</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136">
-        <v>328789</v>
+        <v>327383</v>
       </c>
       <c r="B136">
-        <v>40.1666666666586</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C136">
-        <v>-124.24999999999901</v>
+        <v>-124.29166669999999</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>328790</v>
+        <v>327384</v>
       </c>
       <c r="B137">
-        <v>40.166666669999998</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C137">
-        <v>-124.20833330000001</v>
+        <v>-124.25</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138">
-        <v>328791</v>
+        <v>327385</v>
       </c>
       <c r="B138">
-        <v>40.166666669999998</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C138">
-        <v>-124.16666669999999</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139">
-        <v>328792</v>
+        <v>327386</v>
       </c>
       <c r="B139">
-        <v>40.166666669999998</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C139">
-        <v>-124.125</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140">
-        <v>328793</v>
+        <v>327387</v>
       </c>
       <c r="B140">
-        <v>40.166666669999998</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C140">
-        <v>-124.08333330000001</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141">
-        <v>328794</v>
+        <v>327388</v>
       </c>
       <c r="B141">
-        <v>40.166666669999998</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C141">
-        <v>-124.04166669999999</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142">
-        <v>328795</v>
+        <v>327389</v>
       </c>
       <c r="B142">
-        <v>40.166666669999998</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C142">
-        <v>-124</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143">
-        <v>328796</v>
+        <v>327390</v>
       </c>
       <c r="B143">
-        <v>40.166666669999998</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C143">
-        <v>-123.95833330000001</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144">
-        <v>328797</v>
+        <v>327391</v>
       </c>
       <c r="B144">
-        <v>40.166666669999998</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C144">
-        <v>-123.91666669999999</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145">
-        <v>328798</v>
+        <v>327392</v>
       </c>
       <c r="B145">
-        <v>40.166666669999998</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C145">
-        <v>-123.875</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146">
-        <v>328799</v>
+        <v>327393</v>
       </c>
       <c r="B146">
-        <v>40.166666669999998</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C146">
-        <v>-123.83333330000001</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147">
-        <v>328800</v>
+        <v>327394</v>
       </c>
       <c r="B147">
-        <v>40.166666669999998</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C147">
-        <v>-123.79166669999999</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148">
-        <v>328801</v>
+        <v>327395</v>
       </c>
       <c r="B148">
-        <v>40.166666669999998</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C148">
-        <v>-123.75</v>
+        <v>-123.79166669999999</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149">
-        <v>330195</v>
+        <v>327396</v>
       </c>
       <c r="B149">
-        <v>40.1249999999918</v>
+        <v>40.208333330000002</v>
       </c>
       <c r="C149">
-        <v>-124.20833333333201</v>
+        <v>-123.75</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150">
-        <v>330196</v>
+        <v>328788</v>
       </c>
       <c r="B150">
-        <v>40.125</v>
+        <v>40.1666666666586</v>
       </c>
       <c r="C150">
-        <v>-124.16666669999999</v>
+        <v>-124.291666666666</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151">
-        <v>330197</v>
+        <v>328789</v>
       </c>
       <c r="B151">
-        <v>40.125</v>
+        <v>40.1666666666586</v>
       </c>
       <c r="C151">
-        <v>-124.125</v>
+        <v>-124.24999999999901</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152">
-        <v>330198</v>
+        <v>328790</v>
       </c>
       <c r="B152">
-        <v>40.125</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C152">
-        <v>-124.08333330000001</v>
+        <v>-124.20833330000001</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153">
-        <v>330199</v>
+        <v>328791</v>
       </c>
       <c r="B153">
-        <v>40.125</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C153">
-        <v>-124.04166669999999</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154">
-        <v>330200</v>
+        <v>328792</v>
       </c>
       <c r="B154">
-        <v>40.125</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C154">
-        <v>-124</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155">
-        <v>330201</v>
+        <v>328793</v>
       </c>
       <c r="B155">
-        <v>40.125</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C155">
-        <v>-123.95833330000001</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156">
-        <v>330202</v>
+        <v>328794</v>
       </c>
       <c r="B156">
-        <v>40.125</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C156">
-        <v>-123.91666669999999</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157">
-        <v>330203</v>
+        <v>328795</v>
       </c>
       <c r="B157">
-        <v>40.125</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C157">
-        <v>-123.875</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158">
-        <v>330204</v>
+        <v>328796</v>
       </c>
       <c r="B158">
-        <v>40.125</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C158">
-        <v>-123.83333330000001</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159">
-        <v>330205</v>
+        <v>328797</v>
       </c>
       <c r="B159">
-        <v>40.125</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C159">
-        <v>-123.79166669999999</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160">
-        <v>330206</v>
+        <v>328798</v>
       </c>
       <c r="B160">
-        <v>40.125</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C160">
-        <v>-123.75</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161">
-        <v>331601</v>
+        <v>328799</v>
       </c>
       <c r="B161">
-        <v>40.0833333333252</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C161">
-        <v>-124.166666666666</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162">
-        <v>331602</v>
+        <v>328800</v>
       </c>
       <c r="B162">
-        <v>40.0833333333252</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C162">
-        <v>-124.12499999999901</v>
+        <v>-123.79166669999999</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163">
-        <v>331603</v>
+        <v>328801</v>
       </c>
       <c r="B163">
-        <v>40.083333330000002</v>
+        <v>40.166666669999998</v>
       </c>
       <c r="C163">
-        <v>-124.08333330000001</v>
+        <v>-123.75</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164">
-        <v>331604</v>
+        <v>330195</v>
       </c>
       <c r="B164">
-        <v>40.083333330000002</v>
+        <v>40.1249999999918</v>
       </c>
       <c r="C164">
-        <v>-124.04166669999999</v>
+        <v>-124.20833333333201</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165">
-        <v>331605</v>
+        <v>330196</v>
       </c>
       <c r="B165">
-        <v>40.083333330000002</v>
+        <v>40.125</v>
       </c>
       <c r="C165">
-        <v>-124</v>
+        <v>-124.16666669999999</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166">
-        <v>331606</v>
+        <v>330197</v>
       </c>
       <c r="B166">
-        <v>40.083333330000002</v>
+        <v>40.125</v>
       </c>
       <c r="C166">
-        <v>-123.95833330000001</v>
+        <v>-124.125</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167">
-        <v>331607</v>
+        <v>330198</v>
       </c>
       <c r="B167">
-        <v>40.083333330000002</v>
+        <v>40.125</v>
       </c>
       <c r="C167">
-        <v>-123.91666669999999</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168">
-        <v>331608</v>
+        <v>330199</v>
       </c>
       <c r="B168">
-        <v>40.083333330000002</v>
+        <v>40.125</v>
       </c>
       <c r="C168">
-        <v>-123.875</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169">
-        <v>331609</v>
+        <v>330200</v>
       </c>
       <c r="B169">
-        <v>40.083333330000002</v>
+        <v>40.125</v>
       </c>
       <c r="C169">
-        <v>-123.83333330000001</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170">
-        <v>331610</v>
+        <v>330201</v>
       </c>
       <c r="B170">
-        <v>40.083333330000002</v>
+        <v>40.125</v>
       </c>
       <c r="C170">
-        <v>-123.79166669999999</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171">
-        <v>331611</v>
+        <v>330202</v>
       </c>
       <c r="B171">
-        <v>40.083333330000002</v>
+        <v>40.125</v>
       </c>
       <c r="C171">
-        <v>-123.75</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172">
-        <v>333008</v>
+        <v>330203</v>
       </c>
       <c r="B172">
-        <v>40.0416666666585</v>
+        <v>40.125</v>
       </c>
       <c r="C172">
-        <v>-124.08333333333201</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173">
-        <v>333009</v>
+        <v>330204</v>
       </c>
       <c r="B173">
-        <v>40.041666669999998</v>
+        <v>40.125</v>
       </c>
       <c r="C173">
-        <v>-124.04166669999999</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174">
-        <v>333010</v>
+        <v>330205</v>
       </c>
       <c r="B174">
-        <v>40.041666669999998</v>
+        <v>40.125</v>
       </c>
       <c r="C174">
-        <v>-124</v>
+        <v>-123.79166669999999</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175">
-        <v>333011</v>
+        <v>330206</v>
       </c>
       <c r="B175">
-        <v>40.041666669999998</v>
+        <v>40.125</v>
       </c>
       <c r="C175">
-        <v>-123.95833330000001</v>
+        <v>-123.75</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176">
-        <v>333012</v>
+        <v>331601</v>
       </c>
       <c r="B176">
-        <v>40.041666669999998</v>
+        <v>40.0833333333252</v>
       </c>
       <c r="C176">
-        <v>-123.91666669999999</v>
+        <v>-124.166666666666</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177">
-        <v>333013</v>
+        <v>331602</v>
       </c>
       <c r="B177">
-        <v>40.041666669999998</v>
+        <v>40.0833333333252</v>
       </c>
       <c r="C177">
-        <v>-123.875</v>
+        <v>-124.12499999999901</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178">
-        <v>333014</v>
+        <v>331603</v>
       </c>
       <c r="B178">
-        <v>40.041666669999998</v>
+        <v>40.083333330000002</v>
       </c>
       <c r="C178">
-        <v>-123.83333330000001</v>
+        <v>-124.08333330000001</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179">
-        <v>333015</v>
+        <v>331604</v>
       </c>
       <c r="B179">
-        <v>40.041666669999998</v>
+        <v>40.083333330000002</v>
       </c>
       <c r="C179">
-        <v>-123.79166669999999</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180">
-        <v>333016</v>
+        <v>331605</v>
       </c>
       <c r="B180">
-        <v>40.041666669999998</v>
+        <v>40.083333330000002</v>
       </c>
       <c r="C180">
-        <v>-123.75</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181">
-        <v>334414</v>
+        <v>331606</v>
       </c>
       <c r="B181">
-        <v>39.9999999999918</v>
+        <v>40.083333330000002</v>
       </c>
       <c r="C181">
-        <v>-124.04166666666499</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182">
-        <v>334415</v>
+        <v>331607</v>
       </c>
       <c r="B182">
-        <v>40</v>
+        <v>40.083333330000002</v>
       </c>
       <c r="C182">
-        <v>-124</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183">
-        <v>334416</v>
+        <v>331608</v>
       </c>
       <c r="B183">
-        <v>40</v>
+        <v>40.083333330000002</v>
       </c>
       <c r="C183">
-        <v>-123.95833330000001</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184">
-        <v>334417</v>
+        <v>331609</v>
       </c>
       <c r="B184">
-        <v>40</v>
+        <v>40.083333330000002</v>
       </c>
       <c r="C184">
-        <v>-123.91666669999999</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185">
-        <v>334418</v>
+        <v>331610</v>
       </c>
       <c r="B185">
-        <v>40</v>
+        <v>40.083333330000002</v>
       </c>
       <c r="C185">
-        <v>-123.875</v>
+        <v>-123.79166669999999</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186">
-        <v>334419</v>
+        <v>331611</v>
       </c>
       <c r="B186">
-        <v>40</v>
+        <v>40.083333330000002</v>
       </c>
       <c r="C186">
-        <v>-123.83333330000001</v>
+        <v>-123.75</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187">
-        <v>334420</v>
+        <v>333008</v>
       </c>
       <c r="B187">
-        <v>40</v>
+        <v>40.0416666666585</v>
       </c>
       <c r="C187">
-        <v>-123.79166669999999</v>
+        <v>-124.08333333333201</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188">
-        <v>334421</v>
+        <v>333009</v>
       </c>
       <c r="B188">
-        <v>40</v>
+        <v>40.041666669999998</v>
       </c>
       <c r="C188">
-        <v>-123.75</v>
+        <v>-124.04166669999999</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189">
-        <v>334422</v>
+        <v>333010</v>
       </c>
       <c r="B189">
-        <v>40</v>
+        <v>40.041666669999998</v>
       </c>
       <c r="C189">
-        <v>-123.70833330000001</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190">
-        <v>335820</v>
+        <v>333011</v>
       </c>
       <c r="B190">
-        <v>39.958333333325101</v>
+        <v>40.041666669999998</v>
       </c>
       <c r="C190">
-        <v>-123.99999999999901</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191">
-        <v>335821</v>
+        <v>333012</v>
       </c>
       <c r="B191">
-        <v>39.958333330000002</v>
+        <v>40.041666669999998</v>
       </c>
       <c r="C191">
-        <v>-123.95833330000001</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192">
-        <v>335822</v>
+        <v>333013</v>
       </c>
       <c r="B192">
-        <v>39.958333330000002</v>
+        <v>40.041666669999998</v>
       </c>
       <c r="C192">
-        <v>-123.91666669999999</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193">
-        <v>335823</v>
+        <v>333014</v>
       </c>
       <c r="B193">
-        <v>39.958333330000002</v>
+        <v>40.041666669999998</v>
       </c>
       <c r="C193">
-        <v>-123.875</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194">
-        <v>335824</v>
+        <v>333015</v>
       </c>
       <c r="B194">
-        <v>39.958333330000002</v>
+        <v>40.041666669999998</v>
       </c>
       <c r="C194">
-        <v>-123.83333330000001</v>
+        <v>-123.79166669999999</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195">
-        <v>335825</v>
+        <v>333016</v>
       </c>
       <c r="B195">
-        <v>39.958333330000002</v>
+        <v>40.041666669999998</v>
       </c>
       <c r="C195">
-        <v>-123.79166669999999</v>
+        <v>-123.75</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196">
-        <v>335826</v>
+        <v>334414</v>
       </c>
       <c r="B196">
-        <v>39.958333330000002</v>
+        <v>39.9999999999918</v>
       </c>
       <c r="C196">
-        <v>-123.75</v>
+        <v>-124.04166666666499</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197">
-        <v>337226</v>
+        <v>334415</v>
       </c>
       <c r="B197">
-        <v>39.916666669999998</v>
+        <v>40</v>
       </c>
       <c r="C197">
-        <v>-123.95833330000001</v>
+        <v>-124</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198">
-        <v>337227</v>
+        <v>334416</v>
       </c>
       <c r="B198">
-        <v>39.916666669999998</v>
+        <v>40</v>
       </c>
       <c r="C198">
-        <v>-123.91666669999999</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199">
-        <v>337228</v>
+        <v>334417</v>
       </c>
       <c r="B199">
-        <v>39.916666669999998</v>
+        <v>40</v>
       </c>
       <c r="C199">
-        <v>-123.875</v>
+        <v>-123.91666669999999</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200">
-        <v>337229</v>
+        <v>334418</v>
       </c>
       <c r="B200">
-        <v>39.916666669999998</v>
+        <v>40</v>
       </c>
       <c r="C200">
-        <v>-123.83333330000001</v>
+        <v>-123.875</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201">
-        <v>337230</v>
+        <v>334419</v>
       </c>
       <c r="B201">
-        <v>39.916666669999998</v>
+        <v>40</v>
       </c>
       <c r="C201">
-        <v>-123.79166669999999</v>
+        <v>-123.83333330000001</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202">
-        <v>337231</v>
+        <v>334420</v>
       </c>
       <c r="B202">
-        <v>39.916666669999998</v>
+        <v>40</v>
       </c>
       <c r="C202">
-        <v>-123.75</v>
+        <v>-123.79166669999999</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203">
-        <v>338632</v>
+        <v>334421</v>
       </c>
       <c r="B203">
-        <v>39.875</v>
+        <v>40</v>
       </c>
       <c r="C203">
-        <v>-123.91666669999999</v>
+        <v>-123.75</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204">
-        <v>338633</v>
+        <v>334422</v>
       </c>
       <c r="B204">
-        <v>39.875</v>
+        <v>40</v>
       </c>
       <c r="C204">
-        <v>-123.875</v>
+        <v>-123.70833330000001</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205">
-        <v>338634</v>
+        <v>335820</v>
       </c>
       <c r="B205">
-        <v>39.875</v>
+        <v>39.958333333325101</v>
       </c>
       <c r="C205">
-        <v>-123.83333330000001</v>
+        <v>-123.99999999999901</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206">
-        <v>338635</v>
+        <v>335821</v>
       </c>
       <c r="B206">
-        <v>39.875</v>
+        <v>39.958333330000002</v>
       </c>
       <c r="C206">
-        <v>-123.79166669999999</v>
+        <v>-123.95833330000001</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207">
+        <v>335822</v>
+      </c>
+      <c r="B207">
+        <v>39.958333330000002</v>
+      </c>
+      <c r="C207">
+        <v>-123.91666669999999</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <v>335823</v>
+      </c>
+      <c r="B208">
+        <v>39.958333330000002</v>
+      </c>
+      <c r="C208">
+        <v>-123.875</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <v>335824</v>
+      </c>
+      <c r="B209">
+        <v>39.958333330000002</v>
+      </c>
+      <c r="C209">
+        <v>-123.83333330000001</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <v>335825</v>
+      </c>
+      <c r="B210">
+        <v>39.958333330000002</v>
+      </c>
+      <c r="C210">
+        <v>-123.79166669999999</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A211">
+        <v>335826</v>
+      </c>
+      <c r="B211">
+        <v>39.958333330000002</v>
+      </c>
+      <c r="C211">
+        <v>-123.75</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A212">
+        <v>337226</v>
+      </c>
+      <c r="B212">
+        <v>39.916666669999998</v>
+      </c>
+      <c r="C212">
+        <v>-123.95833330000001</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A213">
+        <v>337227</v>
+      </c>
+      <c r="B213">
+        <v>39.916666669999998</v>
+      </c>
+      <c r="C213">
+        <v>-123.91666669999999</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A214">
+        <v>337228</v>
+      </c>
+      <c r="B214">
+        <v>39.916666669999998</v>
+      </c>
+      <c r="C214">
+        <v>-123.875</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215">
+        <v>337229</v>
+      </c>
+      <c r="B215">
+        <v>39.916666669999998</v>
+      </c>
+      <c r="C215">
+        <v>-123.83333330000001</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A216">
+        <v>337230</v>
+      </c>
+      <c r="B216">
+        <v>39.916666669999998</v>
+      </c>
+      <c r="C216">
+        <v>-123.79166669999999</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A217">
+        <v>337231</v>
+      </c>
+      <c r="B217">
+        <v>39.916666669999998</v>
+      </c>
+      <c r="C217">
+        <v>-123.75</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A218">
+        <v>338632</v>
+      </c>
+      <c r="B218">
+        <v>39.875</v>
+      </c>
+      <c r="C218">
+        <v>-123.91666669999999</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A219">
+        <v>338633</v>
+      </c>
+      <c r="B219">
+        <v>39.875</v>
+      </c>
+      <c r="C219">
+        <v>-123.875</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A220">
+        <v>338634</v>
+      </c>
+      <c r="B220">
+        <v>39.875</v>
+      </c>
+      <c r="C220">
+        <v>-123.83333330000001</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A221">
+        <v>338635</v>
+      </c>
+      <c r="B221">
+        <v>39.875</v>
+      </c>
+      <c r="C221">
+        <v>-123.79166669999999</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A222">
         <v>340038</v>
       </c>
-      <c r="B207">
+      <c r="B222">
         <v>39.833333330000002</v>
       </c>
-      <c r="C207">
+      <c r="C222">
         <v>-123.875</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C207" xr:uid="{C6D3A6DD-588C-4514-87BD-3A8DDF36FFF6}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C207">
+  <autoFilter ref="A1:C222" xr:uid="{C6D3A6DD-588C-4514-87BD-3A8DDF36FFF6}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C222">
       <sortCondition ref="A1:A207"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K2:M208">
-    <sortCondition ref="K1:K208"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4693A724-9298-4483-9B9E-D6EAC7997E3D}">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -4895,7 +5549,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>48264</v>
       </c>
@@ -4905,9 +5559,8 @@
       <c r="C2">
         <v>-123.938</v>
       </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>47799</v>
       </c>
@@ -4917,9 +5570,8 @@
       <c r="C3">
         <v>-124.063</v>
       </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>47800</v>
       </c>
@@ -4929,9 +5581,8 @@
       <c r="C4">
         <v>-123.938</v>
       </c>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>47334</v>
       </c>
@@ -4941,9 +5592,8 @@
       <c r="C5">
         <v>-124.188</v>
       </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>47335</v>
       </c>
@@ -4953,9 +5603,8 @@
       <c r="C6">
         <v>-124.063</v>
       </c>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>47333</v>
       </c>
@@ -4965,9 +5614,8 @@
       <c r="C7">
         <v>-124.313</v>
       </c>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>47336</v>
       </c>
@@ -4977,9 +5625,8 @@
       <c r="C8">
         <v>-123.938</v>
       </c>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>47337</v>
       </c>
@@ -4989,9 +5636,8 @@
       <c r="C9">
         <v>-123.813</v>
       </c>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>46869</v>
       </c>
@@ -5001,9 +5647,8 @@
       <c r="C10">
         <v>-124.313</v>
       </c>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>46870</v>
       </c>
@@ -5013,9 +5658,8 @@
       <c r="C11">
         <v>-124.188</v>
       </c>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>46871</v>
       </c>
@@ -5025,9 +5669,8 @@
       <c r="C12">
         <v>-124.063</v>
       </c>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>46872</v>
       </c>
@@ -5037,9 +5680,8 @@
       <c r="C13">
         <v>-123.938</v>
       </c>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>46405</v>
       </c>
@@ -5049,9 +5691,8 @@
       <c r="C14">
         <v>-124.313</v>
       </c>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>46406</v>
       </c>
@@ -5061,9 +5702,8 @@
       <c r="C15">
         <v>-124.188</v>
       </c>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>46407</v>
       </c>
@@ -5073,9 +5713,8 @@
       <c r="C16">
         <v>-124.063</v>
       </c>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>46408</v>
       </c>
@@ -5085,9 +5724,8 @@
       <c r="C17">
         <v>-123.938</v>
       </c>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>46404</v>
       </c>
@@ -5097,9 +5735,8 @@
       <c r="C18">
         <v>-124.438</v>
       </c>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>45940</v>
       </c>
@@ -5109,9 +5746,8 @@
       <c r="C19">
         <v>-124.438</v>
       </c>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>45941</v>
       </c>
@@ -5121,9 +5757,8 @@
       <c r="C20">
         <v>-124.313</v>
       </c>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>45942</v>
       </c>
@@ -5133,9 +5768,8 @@
       <c r="C21">
         <v>-124.188</v>
       </c>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>45477</v>
       </c>
@@ -5145,163 +5779,72 @@
       <c r="C22">
         <v>-124.313</v>
       </c>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>45476</v>
+        <v>45478</v>
       </c>
       <c r="B23">
         <v>40.688000000000002</v>
       </c>
       <c r="C23">
-        <v>-124.438</v>
-      </c>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-124.188</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>45478</v>
+        <v>45943</v>
       </c>
       <c r="B24">
-        <v>40.688000000000002</v>
+        <v>40.563000000000002</v>
       </c>
       <c r="C24">
+        <v>-124.063</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>46873</v>
+      </c>
+      <c r="B25">
+        <v>40.313000000000002</v>
+      </c>
+      <c r="C25">
+        <v>-123.813</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>47798</v>
+      </c>
+      <c r="B26">
+        <v>40.063000000000002</v>
+      </c>
+      <c r="C26">
         <v>-124.188</v>
       </c>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>45943</v>
-      </c>
-      <c r="B25">
-        <v>40.563000000000002</v>
-      </c>
-      <c r="C25">
-        <v>-124.063</v>
-      </c>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>46403</v>
-      </c>
-      <c r="B26">
-        <v>40.438000000000002</v>
-      </c>
-      <c r="C26">
-        <v>-124.563</v>
-      </c>
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>46868</v>
+        <v>47801</v>
       </c>
       <c r="B27">
-        <v>40.313000000000002</v>
+        <v>40.063000000000002</v>
       </c>
       <c r="C27">
-        <v>-124.438</v>
-      </c>
-      <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-123.813</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>46873</v>
+        <v>48265</v>
       </c>
       <c r="B28">
-        <v>40.313000000000002</v>
+        <v>39.938000000000002</v>
       </c>
       <c r="C28">
         <v>-123.813</v>
       </c>
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>47332</v>
-      </c>
-      <c r="B29">
-        <v>40.188000000000002</v>
-      </c>
-      <c r="C29">
-        <v>-124.438</v>
-      </c>
-      <c r="F29" s="2"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>47797</v>
-      </c>
-      <c r="B30">
-        <v>40.063000000000002</v>
-      </c>
-      <c r="C30">
-        <v>-124.313</v>
-      </c>
-      <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>47798</v>
-      </c>
-      <c r="B31">
-        <v>40.063000000000002</v>
-      </c>
-      <c r="C31">
-        <v>-124.188</v>
-      </c>
-      <c r="F31" s="2"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>47801</v>
-      </c>
-      <c r="B32">
-        <v>40.063000000000002</v>
-      </c>
-      <c r="C32">
-        <v>-123.813</v>
-      </c>
-      <c r="F32" s="2"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>48262</v>
-      </c>
-      <c r="B33">
-        <v>39.938000000000002</v>
-      </c>
-      <c r="C33">
-        <v>-124.188</v>
-      </c>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>48263</v>
-      </c>
-      <c r="B34">
-        <v>39.938000000000002</v>
-      </c>
-      <c r="C34">
-        <v>-124.063</v>
-      </c>
-      <c r="F34" s="2"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>48265</v>
-      </c>
-      <c r="B35">
-        <v>39.938000000000002</v>
-      </c>
-      <c r="C35">
-        <v>-123.813</v>
-      </c>
-      <c r="F35" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5310,7 +5853,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20FE041B-EF6E-41A6-8A99-A92639AD9FE0}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="30.33203125" customWidth="1"/>
@@ -5670,6 +6213,38 @@
       </c>
       <c r="J11" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12">
+        <v>40.634680000000003</v>
+      </c>
+      <c r="E12">
+        <v>-124.202</v>
+      </c>
+      <c r="F12">
+        <v>128.9</v>
+      </c>
+      <c r="G12" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="1">
+        <v>44937</v>
+      </c>
+      <c r="I12" s="1">
+        <v>45292</v>
+      </c>
+      <c r="J12" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -7267,15 +7842,8 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EEF8DF2-6913-4D5A-B20B-6B2D0E2288AA}">
-  <dimension ref="A1:C179"/>
+  <dimension ref="A1:C202"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="9.88671875" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" customWidth="1"/>
-    <col min="15" max="15" width="11.6640625" customWidth="1"/>
-    <col min="16" max="16" width="25.109375" customWidth="1"/>
-    <col min="17" max="17" width="25" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -7290,340 +7858,340 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>314741</v>
+        <v>309119</v>
       </c>
       <c r="B2">
-        <v>45942</v>
+        <v>45478</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>314742</v>
+        <v>309120</v>
       </c>
       <c r="B3">
-        <v>45943</v>
+        <v>45478</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>316144</v>
+        <v>310523</v>
       </c>
       <c r="B4">
-        <v>45942</v>
+        <v>45477</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>316145</v>
+        <v>310524</v>
       </c>
       <c r="B5">
-        <v>45942</v>
+        <v>45478</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>316146</v>
+        <v>310525</v>
       </c>
       <c r="B6">
-        <v>45942</v>
+        <v>45478</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>316147</v>
+        <v>310526</v>
       </c>
       <c r="B7">
-        <v>45943</v>
+        <v>45478</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>316148</v>
+        <v>311928</v>
       </c>
       <c r="B8">
-        <v>45943</v>
+        <v>45477</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>316149</v>
+        <v>311929</v>
       </c>
       <c r="B9">
-        <v>45943</v>
+        <v>45478</v>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>316150</v>
+        <v>311930</v>
       </c>
       <c r="B10">
-        <v>45943</v>
+        <v>45478</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>317547</v>
+        <v>311931</v>
       </c>
       <c r="B11">
-        <v>46405</v>
+        <v>45478</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>317548</v>
+        <v>311932</v>
       </c>
       <c r="B12">
-        <v>46405</v>
+        <v>45478</v>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>317549</v>
+        <v>313333</v>
       </c>
       <c r="B13">
-        <v>46406</v>
+        <v>45941</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>317550</v>
+        <v>313334</v>
       </c>
       <c r="B14">
-        <v>46406</v>
+        <v>45942</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>317551</v>
+        <v>313335</v>
       </c>
       <c r="B15">
-        <v>46406</v>
+        <v>45942</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>317552</v>
+        <v>313336</v>
       </c>
       <c r="B16">
-        <v>46407</v>
+        <v>45942</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>317553</v>
+        <v>313337</v>
       </c>
       <c r="B17">
-        <v>46407</v>
+        <v>45943</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>317554</v>
+        <v>314737</v>
       </c>
       <c r="B18">
-        <v>46407</v>
+        <v>45941</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>317555</v>
+        <v>314738</v>
       </c>
       <c r="B19">
-        <v>46408</v>
+        <v>45941</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>317556</v>
+        <v>314739</v>
       </c>
       <c r="B20">
-        <v>46408</v>
+        <v>45942</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>317557</v>
+        <v>314740</v>
       </c>
       <c r="B21">
-        <v>46408</v>
+        <v>45942</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>318951</v>
+        <v>314741</v>
       </c>
       <c r="B22">
-        <v>46405</v>
+        <v>45942</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>318952</v>
+        <v>314742</v>
       </c>
       <c r="B23">
-        <v>46405</v>
+        <v>45943</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>318953</v>
+        <v>316142</v>
       </c>
       <c r="B24">
-        <v>46405</v>
+        <v>45941</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>318954</v>
+        <v>316143</v>
       </c>
       <c r="B25">
-        <v>46406</v>
+        <v>45941</v>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>318955</v>
+        <v>316144</v>
       </c>
       <c r="B26">
-        <v>46406</v>
+        <v>45942</v>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>318956</v>
+        <v>316145</v>
       </c>
       <c r="B27">
-        <v>46406</v>
+        <v>45942</v>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>318957</v>
+        <v>316146</v>
       </c>
       <c r="B28">
-        <v>46407</v>
+        <v>45942</v>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>318958</v>
+        <v>316147</v>
       </c>
       <c r="B29">
-        <v>46407</v>
+        <v>45943</v>
       </c>
       <c r="C29">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>318959</v>
+        <v>316148</v>
       </c>
       <c r="B30">
-        <v>46407</v>
+        <v>45943</v>
       </c>
       <c r="C30">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>318960</v>
+        <v>316149</v>
       </c>
       <c r="B31">
-        <v>46408</v>
+        <v>45943</v>
       </c>
       <c r="C31">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>318961</v>
+        <v>316150</v>
       </c>
       <c r="B32">
-        <v>46408</v>
+        <v>45943</v>
       </c>
       <c r="C32">
         <v>6</v>
@@ -7631,76 +8199,76 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>318962</v>
+        <v>317546</v>
       </c>
       <c r="B33">
-        <v>46408</v>
+        <v>46405</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>318963</v>
+        <v>317547</v>
       </c>
       <c r="B34">
-        <v>46408</v>
+        <v>46405</v>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>320356</v>
+        <v>317548</v>
       </c>
       <c r="B35">
         <v>46405</v>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>320357</v>
+        <v>317549</v>
       </c>
       <c r="B36">
-        <v>46405</v>
+        <v>46406</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>320358</v>
+        <v>317550</v>
       </c>
       <c r="B37">
-        <v>46405</v>
+        <v>46406</v>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>320359</v>
+        <v>317551</v>
       </c>
       <c r="B38">
         <v>46406</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>320360</v>
+        <v>317552</v>
       </c>
       <c r="B39">
-        <v>46406</v>
+        <v>46407</v>
       </c>
       <c r="C39">
         <v>6</v>
@@ -7708,10 +8276,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>320361</v>
+        <v>317553</v>
       </c>
       <c r="B40">
-        <v>46406</v>
+        <v>46407</v>
       </c>
       <c r="C40">
         <v>6</v>
@@ -7719,7 +8287,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>320362</v>
+        <v>317554</v>
       </c>
       <c r="B41">
         <v>46407</v>
@@ -7730,10 +8298,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>320363</v>
+        <v>317555</v>
       </c>
       <c r="B42">
-        <v>46407</v>
+        <v>46408</v>
       </c>
       <c r="C42">
         <v>6</v>
@@ -7741,10 +8309,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>320364</v>
+        <v>317556</v>
       </c>
       <c r="B43">
-        <v>46407</v>
+        <v>46408</v>
       </c>
       <c r="C43">
         <v>6</v>
@@ -7752,7 +8320,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>320365</v>
+        <v>317557</v>
       </c>
       <c r="B44">
         <v>46408</v>
@@ -7763,98 +8331,98 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>320366</v>
+        <v>318951</v>
       </c>
       <c r="B45">
-        <v>46408</v>
+        <v>46405</v>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>320367</v>
+        <v>318952</v>
       </c>
       <c r="B46">
-        <v>46408</v>
+        <v>46405</v>
       </c>
       <c r="C46">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>320368</v>
+        <v>318953</v>
       </c>
       <c r="B47">
-        <v>46408</v>
+        <v>46405</v>
       </c>
       <c r="C47">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>321762</v>
+        <v>318954</v>
       </c>
       <c r="B48">
-        <v>46869</v>
+        <v>46406</v>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>321763</v>
+        <v>318955</v>
       </c>
       <c r="B49">
-        <v>46869</v>
+        <v>46406</v>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>321764</v>
+        <v>318956</v>
       </c>
       <c r="B50">
-        <v>46870</v>
+        <v>46406</v>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>321765</v>
+        <v>318957</v>
       </c>
       <c r="B51">
-        <v>46870</v>
+        <v>46407</v>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>321766</v>
+        <v>318958</v>
       </c>
       <c r="B52">
-        <v>46870</v>
+        <v>46407</v>
       </c>
       <c r="C52">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>321767</v>
+        <v>318959</v>
       </c>
       <c r="B53">
-        <v>46871</v>
+        <v>46407</v>
       </c>
       <c r="C53">
         <v>6</v>
@@ -7862,10 +8430,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>321768</v>
+        <v>318960</v>
       </c>
       <c r="B54">
-        <v>46871</v>
+        <v>46408</v>
       </c>
       <c r="C54">
         <v>6</v>
@@ -7873,10 +8441,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>321769</v>
+        <v>318961</v>
       </c>
       <c r="B55">
-        <v>46871</v>
+        <v>46408</v>
       </c>
       <c r="C55">
         <v>6</v>
@@ -7884,10 +8452,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>321770</v>
+        <v>318962</v>
       </c>
       <c r="B56">
-        <v>46872</v>
+        <v>46408</v>
       </c>
       <c r="C56">
         <v>6</v>
@@ -7895,10 +8463,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>321771</v>
+        <v>318963</v>
       </c>
       <c r="B57">
-        <v>46872</v>
+        <v>46408</v>
       </c>
       <c r="C57">
         <v>6</v>
@@ -7906,32 +8474,32 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>321772</v>
+        <v>320356</v>
       </c>
       <c r="B58">
-        <v>46872</v>
+        <v>46405</v>
       </c>
       <c r="C58">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>321773</v>
+        <v>320357</v>
       </c>
       <c r="B59">
-        <v>46873</v>
+        <v>46405</v>
       </c>
       <c r="C59">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>323167</v>
+        <v>320358</v>
       </c>
       <c r="B60">
-        <v>46869</v>
+        <v>46405</v>
       </c>
       <c r="C60">
         <v>4</v>
@@ -7939,10 +8507,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>323168</v>
+        <v>320359</v>
       </c>
       <c r="B61">
-        <v>46869</v>
+        <v>46406</v>
       </c>
       <c r="C61">
         <v>4</v>
@@ -7950,131 +8518,131 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>323169</v>
+        <v>320360</v>
       </c>
       <c r="B62">
-        <v>46870</v>
+        <v>46406</v>
       </c>
       <c r="C62">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>323170</v>
+        <v>320361</v>
       </c>
       <c r="B63">
-        <v>46870</v>
+        <v>46406</v>
       </c>
       <c r="C63">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>323171</v>
+        <v>320362</v>
       </c>
       <c r="B64">
-        <v>46870</v>
+        <v>46407</v>
       </c>
       <c r="C64">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>323172</v>
+        <v>320363</v>
       </c>
       <c r="B65">
-        <v>46871</v>
+        <v>46407</v>
       </c>
       <c r="C65">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>323173</v>
+        <v>320364</v>
       </c>
       <c r="B66">
-        <v>46871</v>
+        <v>46407</v>
       </c>
       <c r="C66">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>323174</v>
+        <v>320365</v>
       </c>
       <c r="B67">
-        <v>46871</v>
+        <v>46408</v>
       </c>
       <c r="C67">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>323175</v>
+        <v>320366</v>
       </c>
       <c r="B68">
-        <v>46872</v>
+        <v>46408</v>
       </c>
       <c r="C68">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>323176</v>
+        <v>320367</v>
       </c>
       <c r="B69">
-        <v>46872</v>
+        <v>46408</v>
       </c>
       <c r="C69">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>323177</v>
+        <v>320368</v>
       </c>
       <c r="B70">
-        <v>46872</v>
+        <v>46408</v>
       </c>
       <c r="C70">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>323178</v>
+        <v>321762</v>
       </c>
       <c r="B71">
-        <v>46873</v>
+        <v>46869</v>
       </c>
       <c r="C71">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>323179</v>
+        <v>321763</v>
       </c>
       <c r="B72">
-        <v>46873</v>
+        <v>46869</v>
       </c>
       <c r="C72">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>324572</v>
+        <v>321764</v>
       </c>
       <c r="B73">
-        <v>46869</v>
+        <v>46870</v>
       </c>
       <c r="C73">
         <v>4</v>
@@ -8082,10 +8650,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>324573</v>
+        <v>321765</v>
       </c>
       <c r="B74">
-        <v>46869</v>
+        <v>46870</v>
       </c>
       <c r="C74">
         <v>4</v>
@@ -8093,87 +8661,87 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>324574</v>
+        <v>321766</v>
       </c>
       <c r="B75">
         <v>46870</v>
       </c>
       <c r="C75">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>324575</v>
+        <v>321767</v>
       </c>
       <c r="B76">
-        <v>46870</v>
+        <v>46871</v>
       </c>
       <c r="C76">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>324576</v>
+        <v>321768</v>
       </c>
       <c r="B77">
-        <v>46870</v>
+        <v>46871</v>
       </c>
       <c r="C77">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>324577</v>
+        <v>321769</v>
       </c>
       <c r="B78">
         <v>46871</v>
       </c>
       <c r="C78">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>324578</v>
+        <v>321770</v>
       </c>
       <c r="B79">
-        <v>46871</v>
+        <v>46872</v>
       </c>
       <c r="C79">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>324579</v>
+        <v>321771</v>
       </c>
       <c r="B80">
-        <v>46871</v>
+        <v>46872</v>
       </c>
       <c r="C80">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>324580</v>
+        <v>321772</v>
       </c>
       <c r="B81">
         <v>46872</v>
       </c>
       <c r="C81">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>324581</v>
+        <v>321773</v>
       </c>
       <c r="B82">
-        <v>46872</v>
+        <v>46873</v>
       </c>
       <c r="C82">
         <v>3</v>
@@ -8181,98 +8749,98 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>324582</v>
+        <v>323167</v>
       </c>
       <c r="B83">
-        <v>46872</v>
+        <v>46869</v>
       </c>
       <c r="C83">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>324583</v>
+        <v>323168</v>
       </c>
       <c r="B84">
-        <v>46873</v>
+        <v>46869</v>
       </c>
       <c r="C84">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>324584</v>
+        <v>323169</v>
       </c>
       <c r="B85">
-        <v>46873</v>
+        <v>46870</v>
       </c>
       <c r="C85">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>324585</v>
+        <v>323170</v>
       </c>
       <c r="B86">
-        <v>46873</v>
+        <v>46870</v>
       </c>
       <c r="C86">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>325977</v>
+        <v>323171</v>
       </c>
       <c r="B87">
-        <v>47333</v>
+        <v>46870</v>
       </c>
       <c r="C87">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>325978</v>
+        <v>323172</v>
       </c>
       <c r="B88">
-        <v>47333</v>
+        <v>46871</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>325979</v>
+        <v>323173</v>
       </c>
       <c r="B89">
-        <v>47334</v>
+        <v>46871</v>
       </c>
       <c r="C89">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>325980</v>
+        <v>323174</v>
       </c>
       <c r="B90">
-        <v>47334</v>
+        <v>46871</v>
       </c>
       <c r="C90">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>325981</v>
+        <v>323175</v>
       </c>
       <c r="B91">
-        <v>47334</v>
+        <v>46872</v>
       </c>
       <c r="C91">
         <v>9</v>
@@ -8280,142 +8848,142 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>325982</v>
+        <v>323176</v>
       </c>
       <c r="B92">
-        <v>47335</v>
+        <v>46872</v>
       </c>
       <c r="C92">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>325983</v>
+        <v>323177</v>
       </c>
       <c r="B93">
-        <v>47335</v>
+        <v>46872</v>
       </c>
       <c r="C93">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>325984</v>
+        <v>323178</v>
       </c>
       <c r="B94">
-        <v>47335</v>
+        <v>46873</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>325985</v>
+        <v>323179</v>
       </c>
       <c r="B95">
-        <v>47336</v>
+        <v>46873</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>325986</v>
+        <v>324572</v>
       </c>
       <c r="B96">
-        <v>47336</v>
+        <v>46869</v>
       </c>
       <c r="C96">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>325987</v>
+        <v>324573</v>
       </c>
       <c r="B97">
-        <v>47336</v>
+        <v>46869</v>
       </c>
       <c r="C97">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>325988</v>
+        <v>324574</v>
       </c>
       <c r="B98">
-        <v>47337</v>
+        <v>46870</v>
       </c>
       <c r="C98">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>325989</v>
+        <v>324575</v>
       </c>
       <c r="B99">
-        <v>47337</v>
+        <v>46870</v>
       </c>
       <c r="C99">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>325990</v>
+        <v>324576</v>
       </c>
       <c r="B100">
-        <v>47337</v>
+        <v>46870</v>
       </c>
       <c r="C100">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>327383</v>
+        <v>324577</v>
       </c>
       <c r="B101">
-        <v>47333</v>
+        <v>46871</v>
       </c>
       <c r="C101">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>327384</v>
+        <v>324578</v>
       </c>
       <c r="B102">
-        <v>47334</v>
+        <v>46871</v>
       </c>
       <c r="C102">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>327385</v>
+        <v>324579</v>
       </c>
       <c r="B103">
-        <v>47334</v>
+        <v>46871</v>
       </c>
       <c r="C103">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>327386</v>
+        <v>324580</v>
       </c>
       <c r="B104">
-        <v>47334</v>
+        <v>46872</v>
       </c>
       <c r="C104">
         <v>9</v>
@@ -8423,139 +8991,139 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>327387</v>
+        <v>324581</v>
       </c>
       <c r="B105">
-        <v>47335</v>
+        <v>46872</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>327388</v>
+        <v>324582</v>
       </c>
       <c r="B106">
-        <v>47335</v>
+        <v>46872</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>327389</v>
+        <v>324583</v>
       </c>
       <c r="B107">
-        <v>47335</v>
+        <v>46873</v>
       </c>
       <c r="C107">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>327390</v>
+        <v>324584</v>
       </c>
       <c r="B108">
-        <v>47336</v>
+        <v>46873</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>327391</v>
+        <v>324585</v>
       </c>
       <c r="B109">
-        <v>47336</v>
+        <v>46873</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>327392</v>
+        <v>325977</v>
       </c>
       <c r="B110">
-        <v>47336</v>
+        <v>47333</v>
       </c>
       <c r="C110">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>327393</v>
+        <v>325978</v>
       </c>
       <c r="B111">
-        <v>47337</v>
+        <v>47333</v>
       </c>
       <c r="C111">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>327394</v>
+        <v>325979</v>
       </c>
       <c r="B112">
-        <v>47337</v>
+        <v>47334</v>
       </c>
       <c r="C112">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>327395</v>
+        <v>325980</v>
       </c>
       <c r="B113">
-        <v>47337</v>
+        <v>47334</v>
       </c>
       <c r="C113">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>327396</v>
+        <v>325981</v>
       </c>
       <c r="B114">
-        <v>47337</v>
+        <v>47334</v>
       </c>
       <c r="C114">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>328790</v>
+        <v>325982</v>
       </c>
       <c r="B115">
-        <v>47334</v>
+        <v>47335</v>
       </c>
       <c r="C115">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>328791</v>
+        <v>325983</v>
       </c>
       <c r="B116">
-        <v>47334</v>
+        <v>47335</v>
       </c>
       <c r="C116">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>328792</v>
+        <v>325984</v>
       </c>
       <c r="B117">
         <v>47335</v>
@@ -8566,54 +9134,54 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>328793</v>
+        <v>325985</v>
       </c>
       <c r="B118">
-        <v>47335</v>
+        <v>47336</v>
       </c>
       <c r="C118">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>328794</v>
+        <v>325986</v>
       </c>
       <c r="B119">
-        <v>47335</v>
+        <v>47336</v>
       </c>
       <c r="C119">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>328795</v>
+        <v>325987</v>
       </c>
       <c r="B120">
         <v>47336</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>328796</v>
+        <v>325988</v>
       </c>
       <c r="B121">
-        <v>47336</v>
+        <v>47337</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>328797</v>
+        <v>325989</v>
       </c>
       <c r="B122">
-        <v>47336</v>
+        <v>47337</v>
       </c>
       <c r="C122">
         <v>3</v>
@@ -8621,7 +9189,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>328798</v>
+        <v>325990</v>
       </c>
       <c r="B123">
         <v>47337</v>
@@ -8632,54 +9200,54 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>328799</v>
+        <v>327383</v>
       </c>
       <c r="B124">
-        <v>47337</v>
+        <v>47333</v>
       </c>
       <c r="C124">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>328800</v>
+        <v>327384</v>
       </c>
       <c r="B125">
-        <v>47337</v>
+        <v>47334</v>
       </c>
       <c r="C125">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>328801</v>
+        <v>327385</v>
       </c>
       <c r="B126">
-        <v>47337</v>
+        <v>47334</v>
       </c>
       <c r="C126">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>330196</v>
+        <v>327386</v>
       </c>
       <c r="B127">
-        <v>47798</v>
+        <v>47334</v>
       </c>
       <c r="C127">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>330197</v>
+        <v>327387</v>
       </c>
       <c r="B128">
-        <v>47799</v>
+        <v>47335</v>
       </c>
       <c r="C128">
         <v>2</v>
@@ -8687,10 +9255,10 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>330198</v>
+        <v>327388</v>
       </c>
       <c r="B129">
-        <v>47799</v>
+        <v>47335</v>
       </c>
       <c r="C129">
         <v>2</v>
@@ -8698,21 +9266,21 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>330199</v>
+        <v>327389</v>
       </c>
       <c r="B130">
-        <v>47799</v>
+        <v>47335</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>330200</v>
+        <v>327390</v>
       </c>
       <c r="B131">
-        <v>47800</v>
+        <v>47336</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -8720,10 +9288,10 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132">
-        <v>330201</v>
+        <v>327391</v>
       </c>
       <c r="B132">
-        <v>47800</v>
+        <v>47336</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -8731,21 +9299,21 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133">
-        <v>330202</v>
+        <v>327392</v>
       </c>
       <c r="B133">
-        <v>47800</v>
+        <v>47336</v>
       </c>
       <c r="C133">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>330203</v>
+        <v>327393</v>
       </c>
       <c r="B134">
-        <v>47801</v>
+        <v>47337</v>
       </c>
       <c r="C134">
         <v>3</v>
@@ -8753,10 +9321,10 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>330204</v>
+        <v>327394</v>
       </c>
       <c r="B135">
-        <v>47801</v>
+        <v>47337</v>
       </c>
       <c r="C135">
         <v>3</v>
@@ -8764,10 +9332,10 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136">
-        <v>330205</v>
+        <v>327395</v>
       </c>
       <c r="B136">
-        <v>47801</v>
+        <v>47337</v>
       </c>
       <c r="C136">
         <v>3</v>
@@ -8775,10 +9343,10 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>330206</v>
+        <v>327396</v>
       </c>
       <c r="B137">
-        <v>47801</v>
+        <v>47337</v>
       </c>
       <c r="C137">
         <v>3</v>
@@ -8786,263 +9354,263 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138">
-        <v>331603</v>
+        <v>328790</v>
       </c>
       <c r="B138">
-        <v>47799</v>
+        <v>47334</v>
       </c>
       <c r="C138">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139">
-        <v>331604</v>
+        <v>328791</v>
       </c>
       <c r="B139">
-        <v>47799</v>
+        <v>47334</v>
       </c>
       <c r="C139">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140">
-        <v>331605</v>
+        <v>328792</v>
       </c>
       <c r="B140">
-        <v>47800</v>
+        <v>47335</v>
       </c>
       <c r="C140">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141">
-        <v>331606</v>
+        <v>328793</v>
       </c>
       <c r="B141">
-        <v>47800</v>
+        <v>47335</v>
       </c>
       <c r="C141">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142">
-        <v>331607</v>
+        <v>328794</v>
       </c>
       <c r="B142">
-        <v>47800</v>
+        <v>47335</v>
       </c>
       <c r="C142">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143">
-        <v>331608</v>
+        <v>328795</v>
       </c>
       <c r="B143">
-        <v>47801</v>
+        <v>47336</v>
       </c>
       <c r="C143">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144">
-        <v>331609</v>
+        <v>328796</v>
       </c>
       <c r="B144">
-        <v>47801</v>
+        <v>47336</v>
       </c>
       <c r="C144">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145">
-        <v>331610</v>
+        <v>328797</v>
       </c>
       <c r="B145">
-        <v>47801</v>
+        <v>47336</v>
       </c>
       <c r="C145">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146">
-        <v>331611</v>
+        <v>328798</v>
       </c>
       <c r="B146">
-        <v>47801</v>
+        <v>47337</v>
       </c>
       <c r="C146">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147">
-        <v>333009</v>
+        <v>328799</v>
       </c>
       <c r="B147">
-        <v>47799</v>
+        <v>47337</v>
       </c>
       <c r="C147">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148">
-        <v>333010</v>
+        <v>328800</v>
       </c>
       <c r="B148">
-        <v>47800</v>
+        <v>47337</v>
       </c>
       <c r="C148">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149">
-        <v>333011</v>
+        <v>328801</v>
       </c>
       <c r="B149">
-        <v>47800</v>
+        <v>47337</v>
       </c>
       <c r="C149">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150">
-        <v>333012</v>
+        <v>330196</v>
       </c>
       <c r="B150">
-        <v>47800</v>
+        <v>47798</v>
       </c>
       <c r="C150">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151">
-        <v>333013</v>
+        <v>330197</v>
       </c>
       <c r="B151">
-        <v>47801</v>
+        <v>47799</v>
       </c>
       <c r="C151">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152">
-        <v>333014</v>
+        <v>330198</v>
       </c>
       <c r="B152">
-        <v>47801</v>
+        <v>47799</v>
       </c>
       <c r="C152">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153">
-        <v>333015</v>
+        <v>330199</v>
       </c>
       <c r="B153">
-        <v>47801</v>
+        <v>47799</v>
       </c>
       <c r="C153">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154">
-        <v>333016</v>
+        <v>330200</v>
       </c>
       <c r="B154">
-        <v>47801</v>
+        <v>47800</v>
       </c>
       <c r="C154">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155">
-        <v>334415</v>
+        <v>330201</v>
       </c>
       <c r="B155">
-        <v>48264</v>
+        <v>47800</v>
       </c>
       <c r="C155">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156">
-        <v>334416</v>
+        <v>330202</v>
       </c>
       <c r="B156">
-        <v>48264</v>
+        <v>47800</v>
       </c>
       <c r="C156">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157">
-        <v>334417</v>
+        <v>330203</v>
       </c>
       <c r="B157">
-        <v>48264</v>
+        <v>47801</v>
       </c>
       <c r="C157">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158">
-        <v>334418</v>
+        <v>330204</v>
       </c>
       <c r="B158">
-        <v>48265</v>
+        <v>47801</v>
       </c>
       <c r="C158">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159">
-        <v>334419</v>
+        <v>330205</v>
       </c>
       <c r="B159">
-        <v>48265</v>
+        <v>47801</v>
       </c>
       <c r="C159">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160">
-        <v>334420</v>
+        <v>330206</v>
       </c>
       <c r="B160">
-        <v>48265</v>
+        <v>47801</v>
       </c>
       <c r="C160">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161">
-        <v>334421</v>
+        <v>331603</v>
       </c>
       <c r="B161">
-        <v>48265</v>
+        <v>47799</v>
       </c>
       <c r="C161">
         <v>5</v>
@@ -9050,10 +9618,10 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162">
-        <v>334422</v>
+        <v>331604</v>
       </c>
       <c r="B162">
-        <v>48265</v>
+        <v>47799</v>
       </c>
       <c r="C162">
         <v>5</v>
@@ -9061,10 +9629,10 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163">
-        <v>335821</v>
+        <v>331605</v>
       </c>
       <c r="B163">
-        <v>48264</v>
+        <v>47800</v>
       </c>
       <c r="C163">
         <v>5</v>
@@ -9072,10 +9640,10 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164">
-        <v>335822</v>
+        <v>331606</v>
       </c>
       <c r="B164">
-        <v>48264</v>
+        <v>47800</v>
       </c>
       <c r="C164">
         <v>5</v>
@@ -9083,10 +9651,10 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165">
-        <v>335823</v>
+        <v>331607</v>
       </c>
       <c r="B165">
-        <v>48265</v>
+        <v>47800</v>
       </c>
       <c r="C165">
         <v>5</v>
@@ -9094,10 +9662,10 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166">
-        <v>335824</v>
+        <v>331608</v>
       </c>
       <c r="B166">
-        <v>48265</v>
+        <v>47801</v>
       </c>
       <c r="C166">
         <v>5</v>
@@ -9105,10 +9673,10 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167">
-        <v>335825</v>
+        <v>331609</v>
       </c>
       <c r="B167">
-        <v>48265</v>
+        <v>47801</v>
       </c>
       <c r="C167">
         <v>5</v>
@@ -9116,10 +9684,10 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168">
-        <v>335826</v>
+        <v>331610</v>
       </c>
       <c r="B168">
-        <v>48265</v>
+        <v>47801</v>
       </c>
       <c r="C168">
         <v>5</v>
@@ -9127,10 +9695,10 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169">
-        <v>337226</v>
+        <v>331611</v>
       </c>
       <c r="B169">
-        <v>48264</v>
+        <v>47801</v>
       </c>
       <c r="C169">
         <v>5</v>
@@ -9138,10 +9706,10 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170">
-        <v>337227</v>
+        <v>333009</v>
       </c>
       <c r="B170">
-        <v>48264</v>
+        <v>47799</v>
       </c>
       <c r="C170">
         <v>5</v>
@@ -9149,10 +9717,10 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171">
-        <v>337228</v>
+        <v>333010</v>
       </c>
       <c r="B171">
-        <v>48265</v>
+        <v>47800</v>
       </c>
       <c r="C171">
         <v>5</v>
@@ -9160,10 +9728,10 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172">
-        <v>337229</v>
+        <v>333011</v>
       </c>
       <c r="B172">
-        <v>48265</v>
+        <v>47800</v>
       </c>
       <c r="C172">
         <v>5</v>
@@ -9171,10 +9739,10 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173">
-        <v>337230</v>
+        <v>333012</v>
       </c>
       <c r="B173">
-        <v>48265</v>
+        <v>47800</v>
       </c>
       <c r="C173">
         <v>5</v>
@@ -9182,10 +9750,10 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174">
-        <v>337231</v>
+        <v>333013</v>
       </c>
       <c r="B174">
-        <v>48265</v>
+        <v>47801</v>
       </c>
       <c r="C174">
         <v>5</v>
@@ -9193,10 +9761,10 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175">
-        <v>338632</v>
+        <v>333014</v>
       </c>
       <c r="B175">
-        <v>48264</v>
+        <v>47801</v>
       </c>
       <c r="C175">
         <v>5</v>
@@ -9204,10 +9772,10 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176">
-        <v>338633</v>
+        <v>333015</v>
       </c>
       <c r="B176">
-        <v>48265</v>
+        <v>47801</v>
       </c>
       <c r="C176">
         <v>5</v>
@@ -9215,10 +9783,10 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177">
-        <v>338634</v>
+        <v>333016</v>
       </c>
       <c r="B177">
-        <v>48265</v>
+        <v>47801</v>
       </c>
       <c r="C177">
         <v>5</v>
@@ -9226,10 +9794,10 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178">
-        <v>338635</v>
+        <v>334415</v>
       </c>
       <c r="B178">
-        <v>48265</v>
+        <v>48264</v>
       </c>
       <c r="C178">
         <v>5</v>
@@ -9237,12 +9805,265 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179">
+        <v>334416</v>
+      </c>
+      <c r="B179">
+        <v>48264</v>
+      </c>
+      <c r="C179">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <v>334417</v>
+      </c>
+      <c r="B180">
+        <v>48264</v>
+      </c>
+      <c r="C180">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <v>334418</v>
+      </c>
+      <c r="B181">
+        <v>48265</v>
+      </c>
+      <c r="C181">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <v>334419</v>
+      </c>
+      <c r="B182">
+        <v>48265</v>
+      </c>
+      <c r="C182">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <v>334420</v>
+      </c>
+      <c r="B183">
+        <v>48265</v>
+      </c>
+      <c r="C183">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <v>334421</v>
+      </c>
+      <c r="B184">
+        <v>48265</v>
+      </c>
+      <c r="C184">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <v>334422</v>
+      </c>
+      <c r="B185">
+        <v>48265</v>
+      </c>
+      <c r="C185">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <v>335821</v>
+      </c>
+      <c r="B186">
+        <v>48264</v>
+      </c>
+      <c r="C186">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <v>335822</v>
+      </c>
+      <c r="B187">
+        <v>48264</v>
+      </c>
+      <c r="C187">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <v>335823</v>
+      </c>
+      <c r="B188">
+        <v>48265</v>
+      </c>
+      <c r="C188">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <v>335824</v>
+      </c>
+      <c r="B189">
+        <v>48265</v>
+      </c>
+      <c r="C189">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <v>335825</v>
+      </c>
+      <c r="B190">
+        <v>48265</v>
+      </c>
+      <c r="C190">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <v>335826</v>
+      </c>
+      <c r="B191">
+        <v>48265</v>
+      </c>
+      <c r="C191">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <v>337226</v>
+      </c>
+      <c r="B192">
+        <v>48264</v>
+      </c>
+      <c r="C192">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <v>337227</v>
+      </c>
+      <c r="B193">
+        <v>48264</v>
+      </c>
+      <c r="C193">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <v>337228</v>
+      </c>
+      <c r="B194">
+        <v>48265</v>
+      </c>
+      <c r="C194">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <v>337229</v>
+      </c>
+      <c r="B195">
+        <v>48265</v>
+      </c>
+      <c r="C195">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <v>337230</v>
+      </c>
+      <c r="B196">
+        <v>48265</v>
+      </c>
+      <c r="C196">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <v>337231</v>
+      </c>
+      <c r="B197">
+        <v>48265</v>
+      </c>
+      <c r="C197">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <v>338632</v>
+      </c>
+      <c r="B198">
+        <v>48264</v>
+      </c>
+      <c r="C198">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <v>338633</v>
+      </c>
+      <c r="B199">
+        <v>48265</v>
+      </c>
+      <c r="C199">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <v>338634</v>
+      </c>
+      <c r="B200">
+        <v>48265</v>
+      </c>
+      <c r="C200">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <v>338635</v>
+      </c>
+      <c r="B201">
+        <v>48265</v>
+      </c>
+      <c r="C201">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202">
         <v>340038</v>
       </c>
-      <c r="B179">
+      <c r="B202">
         <v>48265</v>
       </c>
-      <c r="C179">
+      <c r="C202">
         <v>5</v>
       </c>
     </row>
@@ -9253,7 +10074,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F810A005-1441-4E1A-8F8C-BD7FCCACD770}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="9.44140625" bestFit="1" customWidth="1"/>
@@ -9380,12 +10201,32 @@
         <v>8.3800000000000008</v>
       </c>
     </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>45478</v>
+      </c>
+      <c r="C12">
+        <v>8.3800000000000008</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD1B9453B0FD26428396C40DDB69C7F0" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="802f121d94e69ef52d0e517f320156b7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="04ff8bd0-14ef-4472-a603-3a4b6f9fed19" xmlns:ns3="84c16208-172a-4eaa-b33e-1408ce0b909e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="52afc94f32e932e2c2aa5cc0dde246b5" ns2:_="" ns3:_="">
     <xsd:import namespace="04ff8bd0-14ef-4472-a603-3a4b6f9fed19"/>
@@ -9618,15 +10459,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"Blank Document","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="84c16208-172a-4eaa-b33e-1408ce0b909e" xsi:nil="true"/>
@@ -9645,16 +10486,15 @@
 </p:properties>
 </file>
 
-<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41E32FE7-C838-46D6-8359-8A7BBC9B619E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E96BF69-B1EB-4515-B4A0-E6542DFE7270}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9673,19 +10513,19 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43BD7F1F-596C-48D7-B49B-C059BD9AD9F3}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06124858-FF52-43B6-9F5F-14F707108C35}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A7D180A-E261-4A2D-8CBC-AEEBF9B497B3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -9702,14 +10542,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41E32FE7-C838-46D6-8359-8A7BBC9B619E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0bb6ca0c-ccb3-428b-9d5f-a9c60cad6645}" enabled="1" method="Standard" siteId="{fe186a25-7d49-41e6-9941-05d2281d36c1}" contentBits="0" removed="0"/>

--- a/W3_LSPC_Watershed/inputs/Project_Control_Mattole.xlsx
+++ b/W3_LSPC_Watershed/inputs/Project_Control_Mattole.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE00D7B-944D-47C0-84D7-D1EF87D4A61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D3F4C0-6892-4B70-B85D-039DB8B45198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24525" yWindow="-16395" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flags" sheetId="10" r:id="rId1"/>
@@ -293,10 +293,10 @@
     <t>LOLETA 1.3 ESE, CA US</t>
   </si>
   <si>
-    <t>../data/shared</t>
+    <t>data/shared</t>
   </si>
   <si>
-    <t>../data/projects/Mattole</t>
+    <t>data/projects/Mattole</t>
   </si>
 </sst>
 </file>
@@ -10218,15 +10218,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD1B9453B0FD26428396C40DDB69C7F0" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="802f121d94e69ef52d0e517f320156b7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="04ff8bd0-14ef-4472-a603-3a4b6f9fed19" xmlns:ns3="84c16208-172a-4eaa-b33e-1408ce0b909e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="52afc94f32e932e2c2aa5cc0dde246b5" ns2:_="" ns3:_="">
     <xsd:import namespace="04ff8bd0-14ef-4472-a603-3a4b6f9fed19"/>
@@ -10459,15 +10450,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"Blank Document","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
-</file>
-
-<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="84c16208-172a-4eaa-b33e-1408ce0b909e" xsi:nil="true"/>
@@ -10486,15 +10478,15 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41E32FE7-C838-46D6-8359-8A7BBC9B619E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"Blank Document","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E96BF69-B1EB-4515-B4A0-E6542DFE7270}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10513,19 +10505,15 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43BD7F1F-596C-48D7-B49B-C059BD9AD9F3}">
-  <ds:schemaRefs/>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41E32FE7-C838-46D6-8359-8A7BBC9B619E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06124858-FF52-43B6-9F5F-14F707108C35}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A7D180A-E261-4A2D-8CBC-AEEBF9B497B3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -10542,6 +10530,18 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06124858-FF52-43B6-9F5F-14F707108C35}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43BD7F1F-596C-48D7-B49B-C059BD9AD9F3}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0bb6ca0c-ccb3-428b-9d5f-a9c60cad6645}" enabled="1" method="Standard" siteId="{fe186a25-7d49-41e6-9941-05d2281d36c1}" contentBits="0" removed="0"/>
